--- a/server/excel/release/quest.xlsx
+++ b/server/excel/release/quest.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2186" uniqueCount="2186">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2187" uniqueCount="2187">
   <si>
     <t xml:space="preserve">ID</t>
   </si>
@@ -370,10 +370,10 @@
     <t xml:space="preserve">0:15:5#0:5:100</t>
   </si>
   <si>
-    <t xml:space="preserve">Anh hùng triệu hoán</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tiến hành 3 Lần anh hùng triệu hoán</t>
+    <t xml:space="preserve">Tướng triệu hoán</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tiến hành 3 Lần tướng triệu hoán</t>
   </si>
   <si>
     <t xml:space="preserve">0:15:10#0:1:20</t>
@@ -463,190 +463,190 @@
     <t xml:space="preserve">0:15:15#0:1:50</t>
   </si>
   <si>
-    <t xml:space="preserve">Nhân vật chính đẳng cấp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nhân vật chính đẳng cấp đạt tới 30 Cấp</t>
+    <t xml:space="preserve">Nhân vật chính cấp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nhân vật chính cấp đạt tới 30 Cấp</t>
   </si>
   <si>
     <t xml:space="preserve">0:0:50000#0:1:500</t>
   </si>
   <si>
-    <t xml:space="preserve">Nhân vật chính đẳng cấp đạt tới 40 Cấp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nhân vật chính đẳng cấp đạt tới 50 Cấp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nhân vật chính đẳng cấp đạt tới 60 Cấp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nhân vật chính đẳng cấp đạt tới 70 Cấp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nhân vật chính đẳng cấp đạt tới 80 Cấp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nhân vật chính đẳng cấp đạt tới 90 Cấp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nhân vật chính đẳng cấp đạt tới 100 Cấp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nhân vật chính đẳng cấp đạt tới 120 Cấp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nhân vật chính đẳng cấp đạt tới 140 Cấp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nhân vật chính đẳng cấp đạt tới 160 Cấp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nhân vật chính đẳng cấp đạt tới 180 Cấp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nhân vật chính đẳng cấp đạt tới 200 Cấp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nhân vật chính đẳng cấp đạt tới 5 Cấp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nhân vật chính đẳng cấp đạt tới 10 Cấp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nhân vật chính đẳng cấp đạt tới 15 Cấp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nhân vật chính đẳng cấp đạt tới 20 Cấp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Anh hùng thăng cấp Ⅰ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trước mắt có được một 30 Cấp anh hùng</t>
+    <t xml:space="preserve">Nhân vật chính cấp đạt tới 40 Cấp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nhân vật chính cấp đạt tới 50 Cấp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nhân vật chính cấp đạt tới 60 Cấp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nhân vật chính cấp đạt tới 70 Cấp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nhân vật chính cấp đạt tới 80 Cấp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nhân vật chính cấp đạt tới 90 Cấp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nhân vật chính cấp đạt tới 100 Cấp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nhân vật chính cấp đạt tới 120 Cấp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nhân vật chính cấp đạt tới 140 Cấp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nhân vật chính cấp đạt tới 160 Cấp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nhân vật chính cấp đạt tới 180 Cấp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nhân vật chính cấp đạt tới 200 Cấp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nhân vật chính cấp đạt tới 5 Cấp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nhân vật chính cấp đạt tới 10 Cấp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nhân vật chính cấp đạt tới 15 Cấp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nhân vật chính cấp đạt tới 20 Cấp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tướng thăng cấp Ⅰ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trước mắt có được một 30 Cấp tướng</t>
   </si>
   <si>
     <t xml:space="preserve">0:0:50000#0:1:100</t>
   </si>
   <si>
-    <t xml:space="preserve">Trước mắt có được ba 40 Cấp anh hùng</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trước mắt có được năm 40 Cấp anh hùng</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trước mắt có được ba 50 Cấp anh hùng</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trước mắt có được năm 50 Cấp anh hùng</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trước mắt có được ba 60 Cấp anh hùng</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trước mắt có được năm 60 Cấp anh hùng</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trước mắt có được ba 80 Cấp anh hùng</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trước mắt có được năm 80 Cấp anh hùng</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trước mắt có được ba 100 Cấp anh hùng</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trước mắt có được năm 100 Cấp anh hùng</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Anh hùng thăng cấp Ⅱ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tính gộp lại thu hoạch được ba 145 Cấp anh hùng</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tính gộp lại thu hoạch được năm 145 Cấp anh hùng</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tính gộp lại thu hoạch được ba 165 Cấp anh hùng</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tính gộp lại thu hoạch được năm 165 Cấp anh hùng</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tính gộp lại thu hoạch được ba 185 Cấp anh hùng</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tính gộp lại thu hoạch được năm 185 Cấp anh hùng</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tính gộp lại thu hoạch được ba 205 Cấp anh hùng</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tính gộp lại thu hoạch được năm 205 Cấp anh hùng</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tính gộp lại thu hoạch được ba 255 Cấp anh hùng</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tính gộp lại thu hoạch được năm 255 Cấp anh hùng</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thu thập 4 Tinh anh hùng</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trước mắt có được một 4 Tinh anh hùng</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trước mắt có được ba 4 Tinh anh hùng</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trước mắt có được năm 4 Tinh anh hùng</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trước mắt có được tám 4 Tinh anh hùng</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trước mắt có được mười 4 Tinh anh hùng</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thu thập 5 sao anh hùng</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trước mắt có được một 5 sao anh hùng</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trước mắt có được ba 5 sao anh hùng</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trước mắt có được năm 5 sao anh hùng</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trước mắt có được tám 5 sao anh hùng</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trước mắt có được mười 5 sao anh hùng</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thu thập 6 sao anh hùng</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tính gộp lại thu hoạch được một 6 sao anh hùng</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tính gộp lại thu hoạch được ba 6 sao anh hùng</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tính gộp lại thu hoạch được năm 6 sao anh hùng</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tính gộp lại thu hoạch được tám 6 sao anh hùng</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tính gộp lại thu hoạch được mười 6 sao anh hùng</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tiến hành 1 Lần anh hùng triệu hoán</t>
+    <t xml:space="preserve">Trước mắt có được ba 40 Cấp tướng</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trước mắt có được năm 40 Cấp tướng</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trước mắt có được ba 50 Cấp tướng</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trước mắt có được năm 50 Cấp tướng</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trước mắt có được ba 60 Cấp tướng</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trước mắt có được năm 60 Cấp tướng</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trước mắt có được ba 80 Cấp tướng</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trước mắt có được năm 80 Cấp tướng</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trước mắt có được ba 100 Cấp tướng</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trước mắt có được năm 100 Cấp tướng</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tướng thăng cấp Ⅱ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tích luỹ nhận được ba 145 Cấp tướng</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tích luỹ nhận được năm 145 Cấp tướng</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tích luỹ nhận được ba 165 Cấp tướng</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tích luỹ nhận được năm 165 Cấp tướng</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tích luỹ nhận được ba 185 Cấp tướng</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tích luỹ nhận được năm 185 Cấp tướng</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tích luỹ nhận được ba 205 Cấp tướng</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tích luỹ nhận được năm 205 Cấp tướng</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tích luỹ nhận được ba 255 Cấp tướng</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tích luỹ nhận được năm 255 Cấp tướng</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thu thập 4 Tinh tướng</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trước mắt có được một 4 Tinh tướng</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trước mắt có được ba 4 Tinh tướng</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trước mắt có được năm 4 Tinh tướng</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trước mắt có được tám 4 Tinh tướng</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trước mắt có được mười 4 Tinh tướng</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thu thập 5 sao tướng</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trước mắt có được một 5 sao tướng</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trước mắt có được ba 5 sao tướng</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trước mắt có được năm 5 sao tướng</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trước mắt có được tám 5 sao tướng</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trước mắt có được mười 5 sao tướng</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thu thập 6 sao tướng</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tích luỹ nhận được một 6 sao tướng</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tích luỹ nhận được ba 6 sao tướng</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tích luỹ nhận được năm 6 sao tướng</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tích luỹ nhận được tám 6 sao tướng</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tích luỹ nhận được mười 6 sao tướng</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tiến hành 1 Lần tướng triệu hoán</t>
   </si>
   <si>
     <t xml:space="preserve">0:15:10#0:1:30</t>
@@ -685,7 +685,7 @@
     <t xml:space="preserve">Tiến hành 100 Lần cao cấp triệu hoán</t>
   </si>
   <si>
-    <t xml:space="preserve">Lại tiến hành 1 Lần anh hùng triệu hoán</t>
+    <t xml:space="preserve">Lại tiến hành 1 Lần tướng triệu hoán</t>
   </si>
   <si>
     <t xml:space="preserve">0:0:50000</t>
@@ -724,112 +724,112 @@
     <t xml:space="preserve">Tiến hành 100 Lần mời rượu</t>
   </si>
   <si>
-    <t xml:space="preserve">Anh hùng phân giải</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tính gộp lại phân giải 10 Anh hùng</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tính gộp lại phân giải 20 Anh hùng</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tính gộp lại phân giải 30 Anh hùng</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tính gộp lại phân giải 40 Anh hùng</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tính gộp lại phân giải 50 Anh hùng</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tính gộp lại phân giải 60 Anh hùng</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tính gộp lại phân giải 70 Anh hùng</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tính gộp lại phân giải 80 Anh hùng</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tính gộp lại phân giải 90 Anh hùng</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tính gộp lại phân giải 100 Anh hùng</t>
+    <t xml:space="preserve">Tướng phân giải</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tích luỹ phân giải 10 Tướng</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tích luỹ phân giải 20 Tướng</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tích luỹ phân giải 30 Tướng</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tích luỹ phân giải 40 Tướng</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tích luỹ phân giải 50 Tướng</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tích luỹ phân giải 60 Tướng</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tích luỹ phân giải 70 Tướng</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tích luỹ phân giải 80 Tướng</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tích luỹ phân giải 90 Tướng</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tích luỹ phân giải 100 Tướng</t>
   </si>
   <si>
     <t xml:space="preserve">Tăng thêm hảo hữu</t>
   </si>
   <si>
-    <t xml:space="preserve">Tính gộp lại có được một hảo hữu</t>
+    <t xml:space="preserve">Tích luỹ có được một hảo hữu</t>
   </si>
   <si>
     <t xml:space="preserve">0:0:50000#0:1:100#3:100002:4</t>
   </si>
   <si>
-    <t xml:space="preserve">Tính gộp lại có được 20 Cái hảo hữu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tính gộp lại có được 30 Cái hảo hữu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tính gộp lại có được 40 Cái hảo hữu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tính gộp lại có được 50 Cái hảo hữu</t>
+    <t xml:space="preserve">Tích luỹ có được 20 Cái hảo hữu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tích luỹ có được 30 Cái hảo hữu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tích luỹ có được 40 Cái hảo hữu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tích luỹ có được 50 Cái hảo hữu</t>
   </si>
   <si>
     <t xml:space="preserve">Trang bị thu thập Ⅰ</t>
   </si>
   <si>
-    <t xml:space="preserve">Tính gộp lại thu hoạch được 4 Kiện tử sắc phẩm chất trang bị</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tính gộp lại thu hoạch được 8 Kiện tử sắc phẩm chất trang bị</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tính gộp lại thu hoạch được 12 Kiện tử sắc phẩm chất trang bị</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tính gộp lại thu hoạch được 16 Kiện tử sắc phẩm chất trang bị</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tính gộp lại thu hoạch được 20 Kiện tử sắc phẩm chất trang bị</t>
+    <t xml:space="preserve">Tích luỹ nhận được 4 Kiện tử sắc phẩm chất trang bị</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tích luỹ nhận được 8 Kiện tử sắc phẩm chất trang bị</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tích luỹ nhận được 12 Kiện tử sắc phẩm chất trang bị</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tích luỹ nhận được 16 Kiện tử sắc phẩm chất trang bị</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tích luỹ nhận được 20 Kiện tử sắc phẩm chất trang bị</t>
   </si>
   <si>
     <t xml:space="preserve">Trang bị thu thập Ⅱ</t>
   </si>
   <si>
-    <t xml:space="preserve">Tính gộp lại thu hoạch được 4 Kiện màu cam phẩm chất trang bị</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tính gộp lại thu hoạch được 8 Kiện màu cam phẩm chất trang bị</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tính gộp lại thu hoạch được 12 Kiện màu cam phẩm chất trang bị</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tính gộp lại thu hoạch được 16 Kiện màu cam phẩm chất trang bị</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tính gộp lại thu hoạch được 20 Kiện màu cam phẩm chất trang bị</t>
+    <t xml:space="preserve">Tích luỹ nhận được 4 Kiện màu cam phẩm chất trang bị</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tích luỹ nhận được 8 Kiện màu cam phẩm chất trang bị</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tích luỹ nhận được 12 Kiện màu cam phẩm chất trang bị</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tích luỹ nhận được 16 Kiện màu cam phẩm chất trang bị</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tích luỹ nhận được 20 Kiện màu cam phẩm chất trang bị</t>
   </si>
   <si>
     <t xml:space="preserve">Trang bị thu thập Ⅲ</t>
   </si>
   <si>
-    <t xml:space="preserve">Tính gộp lại thu hoạch được 4 trang bị đỏ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tính gộp lại thu hoạch được 8 trang bị đỏ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tính gộp lại thu hoạch được 12 trang bị đỏ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tính gộp lại thu hoạch được 16 trang bị đỏ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tính gộp lại thu hoạch được 20 trang bị đỏ</t>
+    <t xml:space="preserve">Tích luỹ nhận được 4 trang bị đỏ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tích luỹ nhận được 8 trang bị đỏ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tích luỹ nhận được 12 trang bị đỏ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tích luỹ nhận được 16 trang bị đỏ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tích luỹ nhận được 20 trang bị đỏ</t>
   </si>
   <si>
     <t xml:space="preserve">hợp thiên phú</t>
@@ -913,85 +913,85 @@
     <t xml:space="preserve">Đấu trường mỗi ngày kết toán lúc xếp hạng thứ 1 Tên</t>
   </si>
   <si>
-    <t xml:space="preserve">Tính gộp lại khiêu chiến 10 Ngày kế tiếp thường phó bản</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tính gộp lại khiêu chiến 30 Ngày kế tiếp thường phó bản</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tính gộp lại khiêu chiến 50 Ngày kế tiếp thường phó bản</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tính gộp lại khiêu chiến 80 Ngày kế tiếp thường phó bản</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tính gộp lại khiêu chiến 100 Ngày kế tiếp thường phó bản</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tính gộp lại khiêu chiến 200 Ngày kế tiếp thường phó bản</t>
+    <t xml:space="preserve">Tích luỹ khiêu chiến 10 Ngày kế tiếp thường phó bản</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tích luỹ khiêu chiến 30 Ngày kế tiếp thường phó bản</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tích luỹ khiêu chiến 50 Ngày kế tiếp thường phó bản</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tích luỹ khiêu chiến 80 Ngày kế tiếp thường phó bản</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tích luỹ khiêu chiến 100 Ngày kế tiếp thường phó bản</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tích luỹ khiêu chiến 200 Ngày kế tiếp thường phó bản</t>
   </si>
   <si>
     <t xml:space="preserve">thưởng thiện phạt ác Ⅰ</t>
   </si>
   <si>
-    <t xml:space="preserve">Tính gộp lại xác nhận 10 Lần tử sắc phẩm chất nhiệm vụ</t>
+    <t xml:space="preserve">Tích luỹ xác nhận 10 Lần tử sắc phẩm chất nhiệm vụ</t>
   </si>
   <si>
     <t xml:space="preserve">0:0:50000#3:100008:10</t>
   </si>
   <si>
-    <t xml:space="preserve">Tính gộp lại xác nhận 30 Lần tử sắc phẩm chất nhiệm vụ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tính gộp lại xác nhận 50 Lần tử sắc phẩm chất nhiệm vụ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tính gộp lại xác nhận 70 Lần tử sắc phẩm chất nhiệm vụ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tính gộp lại xác nhận 100 Lần tử sắc phẩm chất nhiệm vụ</t>
+    <t xml:space="preserve">Tích luỹ xác nhận 30 Lần tử sắc phẩm chất nhiệm vụ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tích luỹ xác nhận 50 Lần tử sắc phẩm chất nhiệm vụ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tích luỹ xác nhận 70 Lần tử sắc phẩm chất nhiệm vụ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tích luỹ xác nhận 100 Lần tử sắc phẩm chất nhiệm vụ</t>
   </si>
   <si>
     <t xml:space="preserve">thưởng thiện phạt ác Ⅱ</t>
   </si>
   <si>
-    <t xml:space="preserve">Tính gộp lại xác nhận 5 Lần màu cam phẩm chất nhiệm vụ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tính gộp lại xác nhận 15 Lần màu cam phẩm chất nhiệm vụ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tính gộp lại xác nhận 30 Lần màu cam phẩm chất nhiệm vụ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tính gộp lại xác nhận 50 Lần màu cam phẩm chất nhiệm vụ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tính gộp lại xác nhận 75 Lần màu cam phẩm chất nhiệm vụ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tính gộp lại xác nhận 100 Lần màu cam phẩm chất nhiệm vụ</t>
+    <t xml:space="preserve">Tích luỹ xác nhận 5 Lần màu cam phẩm chất nhiệm vụ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tích luỹ xác nhận 15 Lần màu cam phẩm chất nhiệm vụ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tích luỹ xác nhận 30 Lần màu cam phẩm chất nhiệm vụ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tích luỹ xác nhận 50 Lần màu cam phẩm chất nhiệm vụ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tích luỹ xác nhận 75 Lần màu cam phẩm chất nhiệm vụ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tích luỹ xác nhận 100 Lần màu cam phẩm chất nhiệm vụ</t>
   </si>
   <si>
     <t xml:space="preserve">thưởng thiện phạt ác Ⅲ</t>
   </si>
   <si>
-    <t xml:space="preserve">Tính gộp lại xác nhận 5 Lần màu đỏ phẩm chất nhiệm vụ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tính gộp lại xác nhận 15 Lần màu đỏ phẩm chất nhiệm vụ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tính gộp lại xác nhận 30 Lần màu đỏ phẩm chất nhiệm vụ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tính gộp lại xác nhận 50 Lần màu đỏ phẩm chất nhiệm vụ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tính gộp lại xác nhận 75 Lần màu đỏ phẩm chất nhiệm vụ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tính gộp lại xác nhận 100 Lần màu đỏ phẩm chất nhiệm vụ</t>
+    <t xml:space="preserve">Tích luỹ xác nhận 5 Lần màu đỏ phẩm chất nhiệm vụ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tích luỹ xác nhận 15 Lần màu đỏ phẩm chất nhiệm vụ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tích luỹ xác nhận 30 Lần màu đỏ phẩm chất nhiệm vụ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tích luỹ xác nhận 50 Lần màu đỏ phẩm chất nhiệm vụ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tích luỹ xác nhận 75 Lần màu đỏ phẩm chất nhiệm vụ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tích luỹ xác nhận 100 Lần màu đỏ phẩm chất nhiệm vụ</t>
   </si>
   <si>
     <t xml:space="preserve">Võ lâm luận kiếm ( Tùy ý độ khó ) Lịch sử tối cao thông quan đạt tới 5 Quan</t>
@@ -1015,61 +1015,61 @@
     <t xml:space="preserve">Khiêu chiến guild phó bản</t>
   </si>
   <si>
-    <t xml:space="preserve">Tính gộp lại khiêu chiến 1 Lần guild phó bản</t>
+    <t xml:space="preserve">Tích luỹ khiêu chiến 1 Lần guild phó bản</t>
   </si>
   <si>
     <t xml:space="preserve">0:0:50000#0:12:100</t>
   </si>
   <si>
-    <t xml:space="preserve">Tính gộp lại khiêu chiến 2 Lần guild phó bản</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tính gộp lại khiêu chiến 10 Lần guild phó bản</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tính gộp lại khiêu chiến 30 Lần guild phó bản</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tính gộp lại khiêu chiến 50 Lần guild phó bản</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tính gộp lại khiêu chiến 80 Lần guild phó bản</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tính gộp lại khiêu chiến 100 Lần guild phó bản</t>
+    <t xml:space="preserve">Tích luỹ khiêu chiến 2 Lần guild phó bản</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tích luỹ khiêu chiến 10 Lần guild phó bản</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tích luỹ khiêu chiến 30 Lần guild phó bản</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tích luỹ khiêu chiến 50 Lần guild phó bản</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tích luỹ khiêu chiến 80 Lần guild phó bản</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tích luỹ khiêu chiến 100 Lần guild phó bản</t>
   </si>
   <si>
     <t xml:space="preserve">Đánh giết guild phó bản Boss</t>
   </si>
   <si>
-    <t xml:space="preserve">Tính gộp lại đánh giết 1 Lần guild phó bản Boss</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tính gộp lại đánh giết 3 Lần guild phó bản Boss</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tính gộp lại đánh giết 5 Lần guild phó bản Boss</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tính gộp lại đánh giết 10 Lần guild phó bản Boss</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tính gộp lại đánh giết 20 Lần guild phó bản Boss</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thu thập 9 sao anh hùng</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trước mắt có được một 9 sao anh hùng</t>
+    <t xml:space="preserve">Tích luỹ đánh giết 1 Lần guild phó bản Boss</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tích luỹ đánh giết 3 Lần guild phó bản Boss</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tích luỹ đánh giết 5 Lần guild phó bản Boss</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tích luỹ đánh giết 10 Lần guild phó bản Boss</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tích luỹ đánh giết 20 Lần guild phó bản Boss</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thu thập 9 sao tướng</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trước mắt có được một 9 sao tướng</t>
   </si>
   <si>
     <t xml:space="preserve">2:19000315:1#2:19000415:1</t>
   </si>
   <si>
-    <t xml:space="preserve">Thu thập 10 sao anh hùng</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trước mắt có được một 10 sao anh hùng</t>
+    <t xml:space="preserve">Thu thập 10 sao tướng</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trước mắt có được một 10 sao tướng</t>
   </si>
   <si>
     <t xml:space="preserve">2:19000115:1#2:19000215:1</t>
@@ -1105,19 +1105,19 @@
     <t xml:space="preserve">Lấy yếu thắng mạnh Ⅰ</t>
   </si>
   <si>
-    <t xml:space="preserve">Tại PVP Chiến đấu bên trong, chiến thắng chiến lực cao hơn tự thân 10 Vạn đối thủ 20 Lần</t>
+    <t xml:space="preserve">Tại PVP Chiến đấu bên trong, chiến thắng chiến lực cao hơn tự thân 100K đối thủ 20 Lần</t>
   </si>
   <si>
     <t xml:space="preserve">Lấy yếu thắng mạnh Ⅱ</t>
   </si>
   <si>
-    <t xml:space="preserve">Tại PVP Chiến đấu bên trong, chiến thắng chiến lực cao hơn tự thân 20 Vạn đối thủ 15 Lần</t>
+    <t xml:space="preserve">Tại PVP Chiến đấu bên trong, chiến thắng chiến lực cao hơn tự thân 200K đối thủ 15 Lần</t>
   </si>
   <si>
     <t xml:space="preserve">Lấy yếu thắng mạnh Ⅲ</t>
   </si>
   <si>
-    <t xml:space="preserve">Tại PVP Chiến đấu bên trong, chiến thắng chiến lực cao hơn tự thân 30 Vạn đối thủ 10 Lần</t>
+    <t xml:space="preserve">Tại PVP Chiến đấu bên trong, chiến thắng chiến lực cao hơn tự thân 300K đối thủ 10 Lần</t>
   </si>
   <si>
     <t xml:space="preserve">Toàn thắng</t>
@@ -1129,25 +1129,25 @@
     <t xml:space="preserve">thần binh đánh giết</t>
   </si>
   <si>
-    <t xml:space="preserve">Tại PVP Chiến đấu bên trong, sử dụng thần binh tính gộp lại đánh giết địch quân anh hùng 100 Lần</t>
+    <t xml:space="preserve">Tại PVP Chiến đấu bên trong, sử dụng thần binh tích luỹ đánh giết địch quân tướng 100 Lần</t>
   </si>
   <si>
     <t xml:space="preserve">thần binh khống chế</t>
   </si>
   <si>
-    <t xml:space="preserve">Tại PVP Chiến đấu bên trong, sử dụng Hạo Thiên Chùy tính gộp lại mê muội 200 Cái địch quân anh hùng</t>
+    <t xml:space="preserve">Tại PVP Chiến đấu bên trong, sử dụng Hạo Thiên Chùy tích luỹ mê muội 200 Cái địch quân tướng</t>
   </si>
   <si>
     <t xml:space="preserve">Đại cứu tinh</t>
   </si>
   <si>
-    <t xml:space="preserve">Tại đơn trận PVP Chiến đấu bên trong sử dụng kỹ năng chủ động phục sinh phe mình anh hùng 3 Lần</t>
+    <t xml:space="preserve">Tại đơn trận PVP Chiến đấu bên trong sử dụng kỹ năng chủ động phục sinh phe mình tướng 3 Lần</t>
   </si>
   <si>
     <t xml:space="preserve">Diệu thủ hồi xuân</t>
   </si>
   <si>
-    <t xml:space="preserve">Tại đơn trận PVP Chiến đấu bên trong tổng trị liệu lượng đạt tới 500 Vạn</t>
+    <t xml:space="preserve">Tại đơn trận PVP Chiến đấu bên trong tổng trị liệu lượng đạt tới 5M</t>
   </si>
   <si>
     <t xml:space="preserve">thông thiên tháp Ⅰ</t>
@@ -1234,22 +1234,22 @@
     <t xml:space="preserve">Tùy ý 1 Loại Thí luyện đạt cao nhất 10</t>
   </si>
   <si>
-    <t xml:space="preserve">Thí luyện xếp hạng Ⅰ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tính gộp lại tiến vào Thí luyện bảng xếp hạng trước 10 Tên 3 Lần</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thí luyện xếp hạng Ⅱ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tính gộp lại tiến vào Thí luyện bảng xếp hạng trước 3 Tên 3 Lần</t>
+    <t xml:space="preserve">Thí luyện xếp hạng Ⅰ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tích luỹ tiến vào Thí luyện bảng xếp hạng trước 10 Tên 3 Lần</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thí luyện xếp hạng Ⅱ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tích luỹ tiến vào Thí luyện bảng xếp hạng trước 3 Tên 3 Lần</t>
   </si>
   <si>
     <t xml:space="preserve">Chiến lực đột phá</t>
   </si>
   <si>
-    <t xml:space="preserve">Sức chiến đấu cao nhất đạt tới 4 Vạn</t>
+    <t xml:space="preserve">Sức chiến đấu cao nhất đạt tới 40K</t>
   </si>
   <si>
     <t xml:space="preserve">3:100025:1#0:1:100</t>
@@ -1258,178 +1258,178 @@
     <t xml:space="preserve">Chiến lực đột phá Ⅰ</t>
   </si>
   <si>
-    <t xml:space="preserve">Sức chiến đấu cao nhất đạt tới 50 Vạn</t>
+    <t xml:space="preserve">Sức chiến đấu cao nhất đạt tới 500K</t>
   </si>
   <si>
     <t xml:space="preserve">Chiến lực đột phá Ⅱ</t>
   </si>
   <si>
-    <t xml:space="preserve">Sức chiến đấu cao nhất đạt tới 100 Vạn</t>
+    <t xml:space="preserve">Sức chiến đấu cao nhất đạt tới 1M</t>
   </si>
   <si>
     <t xml:space="preserve">Chiến lực đột phá Ⅲ</t>
   </si>
   <si>
-    <t xml:space="preserve">Sức chiến đấu cao nhất đạt tới 200 Vạn</t>
+    <t xml:space="preserve">Sức chiến đấu cao nhất đạt tới 2M</t>
   </si>
   <si>
     <t xml:space="preserve">Chiến lực đột phá x</t>
   </si>
   <si>
-    <t xml:space="preserve">Sức chiến đấu cao nhất đạt tới 10 Vạn</t>
+    <t xml:space="preserve">Sức chiến đấu cao nhất đạt tới 100K</t>
   </si>
   <si>
     <t xml:space="preserve">Chiến lực đột phá x1</t>
   </si>
   <si>
-    <t xml:space="preserve">Sức chiến đấu cao nhất đạt tới 20 Vạn</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sức chiến đấu cao nhất đạt tới 15 Vạn</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cứu cực thể anh hùng</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trước mắt có được năm 10 sao anh hùng</t>
+    <t xml:space="preserve">Sức chiến đấu cao nhất đạt tới 200K</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sức chiến đấu cao nhất đạt tới 150K</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cứu cực thể tướng</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trước mắt có được năm 10 sao tướng</t>
   </si>
   <si>
     <t xml:space="preserve">Cứu cực thể · Tân binh</t>
   </si>
   <si>
-    <t xml:space="preserve">Tính gộp lại thu hoạch được một 10 sao Tân binh anh hùng</t>
+    <t xml:space="preserve">Tích luỹ nhận được một 10 sao Tân binh tướng</t>
   </si>
   <si>
     <t xml:space="preserve">Cứu cực thể · Hải tặc</t>
   </si>
   <si>
-    <t xml:space="preserve">Tính gộp lại thu hoạch được một 10 sao Hải tặc anh hùng</t>
+    <t xml:space="preserve">Tích luỹ nhận được một 10 sao Hải tặc tướng</t>
   </si>
   <si>
     <t xml:space="preserve">Cứu cực thể · Dũng sĩ</t>
   </si>
   <si>
-    <t xml:space="preserve">Tính gộp lại thu hoạch được một 10 sao Dũng sĩ anh hùng</t>
+    <t xml:space="preserve">Tích luỹ nhận được một 10 sao Dũng sĩ tướng</t>
   </si>
   <si>
     <t xml:space="preserve">Cứu cực thể · Hải quân</t>
   </si>
   <si>
-    <t xml:space="preserve">Tính gộp lại thu hoạch được một 10 sao Hải quân anh hùng</t>
+    <t xml:space="preserve">Tích luỹ nhận được một 10 sao Hải quân tướng</t>
   </si>
   <si>
     <t xml:space="preserve">Cứu cực thể · Ngũ hoàng</t>
   </si>
   <si>
-    <t xml:space="preserve">Tính gộp lại thu hoạch được một 10 sao Ngũ hoàng anh hùng</t>
+    <t xml:space="preserve">Tích luỹ nhận được một 10 sao Ngũ hoàng tướng</t>
   </si>
   <si>
     <t xml:space="preserve">Thiên phú lĩnh ngộ Ⅰ</t>
   </si>
   <si>
-    <t xml:space="preserve">Tính gộp lại lĩnh ngộ mười sơ cấp thiên phú</t>
+    <t xml:space="preserve">Tích luỹ lĩnh ngộ mười sơ cấp thiên phú</t>
   </si>
   <si>
     <t xml:space="preserve">Thiên phú lĩnh ngộ Ⅱ</t>
   </si>
   <si>
-    <t xml:space="preserve">Tính gộp lại lĩnh ngộ mười trung cấp thiên phú</t>
+    <t xml:space="preserve">Tích luỹ lĩnh ngộ mười trung cấp thiên phú</t>
   </si>
   <si>
     <t xml:space="preserve">Thiên phú lĩnh ngộ Ⅲ</t>
   </si>
   <si>
-    <t xml:space="preserve">Tính gộp lại lĩnh ngộ mười cao cấp thiên phú</t>
+    <t xml:space="preserve">Tích luỹ lĩnh ngộ mười cao cấp thiên phú</t>
   </si>
   <si>
     <t xml:space="preserve">Độc thương tinh thông Ⅰ</t>
   </si>
   <si>
-    <t xml:space="preserve">Đơn cuộc chiến đấu tính gộp lại tạo thành 150 Vạn điểm trúng độc tổn thương</t>
+    <t xml:space="preserve">Đơn cuộc chiến đấu tích luỹ tạo thành 1,5M điểm trúng độc tổn thương</t>
   </si>
   <si>
     <t xml:space="preserve">Độc thương tinh thông Ⅱ</t>
   </si>
   <si>
-    <t xml:space="preserve">Đơn cuộc chiến đấu tính gộp lại tạo thành 200 Vạn điểm trúng độc tổn thương</t>
+    <t xml:space="preserve">Đơn cuộc chiến đấu tích luỹ tạo thành 2M điểm trúng độc tổn thương</t>
   </si>
   <si>
     <t xml:space="preserve">Độc thương tinh thông Ⅲ</t>
   </si>
   <si>
-    <t xml:space="preserve">Đơn cuộc chiến đấu tính gộp lại tạo thành 300 Vạn điểm trúng độc tổn thương</t>
+    <t xml:space="preserve">Đơn cuộc chiến đấu tích luỹ tạo thành 3M điểm trúng độc tổn thương</t>
   </si>
   <si>
     <t xml:space="preserve">Thiêu đốt tinh thông Ⅰ</t>
   </si>
   <si>
-    <t xml:space="preserve">Đơn cuộc chiến đấu tính gộp lại tạo thành 150 Vạn điểm thiêu đốt tổn thương</t>
+    <t xml:space="preserve">Đơn cuộc chiến đấu tích luỹ tạo thành 1,5M điểm thiêu đốt tổn thương</t>
   </si>
   <si>
     <t xml:space="preserve">Thiêu đốt tinh thông Ⅱ</t>
   </si>
   <si>
-    <t xml:space="preserve">Đơn cuộc chiến đấu tính gộp lại tạo thành 200 Vạn điểm thiêu đốt tổn thương</t>
+    <t xml:space="preserve">Đơn cuộc chiến đấu tích luỹ tạo thành 2M điểm thiêu đốt tổn thương</t>
   </si>
   <si>
     <t xml:space="preserve">Thiêu đốt tinh thông Ⅲ</t>
   </si>
   <si>
-    <t xml:space="preserve">Đơn cuộc chiến đấu tính gộp lại tạo thành 300 Vạn điểm thiêu đốt tổn thương</t>
+    <t xml:space="preserve">Đơn cuộc chiến đấu tích luỹ tạo thành 3M điểm thiêu đốt tổn thương</t>
   </si>
   <si>
     <t xml:space="preserve">Chảy máu tinh thông Ⅰ</t>
   </si>
   <si>
-    <t xml:space="preserve">Đơn cuộc chiến đấu tính gộp lại tạo thành 150 Vạn điểm chảy máu tổn thương</t>
+    <t xml:space="preserve">Đơn cuộc chiến đấu tích luỹ tạo thành 1,5M điểm chảy máu tổn thương</t>
   </si>
   <si>
     <t xml:space="preserve">Chảy máu tinh thông Ⅱ</t>
   </si>
   <si>
-    <t xml:space="preserve">Đơn cuộc chiến đấu tính gộp lại tạo thành 200 Vạn điểm chảy máu tổn thương</t>
+    <t xml:space="preserve">Đơn cuộc chiến đấu tích luỹ tạo thành 2M điểm chảy máu tổn thương</t>
   </si>
   <si>
     <t xml:space="preserve">Chảy máu tinh thông Ⅲ</t>
   </si>
   <si>
-    <t xml:space="preserve">Đơn cuộc chiến đấu tính gộp lại tạo thành 300 Vạn điểm chảy máu tổn thương</t>
+    <t xml:space="preserve">Đơn cuộc chiến đấu tích luỹ tạo thành 3M điểm chảy máu tổn thương</t>
   </si>
   <si>
     <t xml:space="preserve">Hỏa lực chuyển vận Ⅰ</t>
   </si>
   <si>
-    <t xml:space="preserve">Đơn trận guild phó bản chiến đấu bên trong tính gộp lại tạo thành 150 Vạn điểm tổn thương</t>
+    <t xml:space="preserve">Đơn trận guild phó bản chiến đấu bên trong tích luỹ tạo thành 1,5M điểm tổn thương</t>
   </si>
   <si>
     <t xml:space="preserve">Hỏa lực chuyển vận Ⅱ</t>
   </si>
   <si>
-    <t xml:space="preserve">Đơn trận guild phó bản chiến đấu bên trong tính gộp lại tạo thành 200 Vạn điểm tổn thương</t>
+    <t xml:space="preserve">Đơn trận guild phó bản chiến đấu bên trong tích luỹ tạo thành 2M điểm tổn thương</t>
   </si>
   <si>
     <t xml:space="preserve">Hỏa lực chuyển vận Ⅲ</t>
   </si>
   <si>
-    <t xml:space="preserve">Đơn trận guild phó bản chiến đấu bên trong tính gộp lại tạo thành 300 Vạn điểm tổn thương</t>
+    <t xml:space="preserve">Đơn trận guild phó bản chiến đấu bên trong tích luỹ tạo thành 3M điểm tổn thương</t>
   </si>
   <si>
     <t xml:space="preserve">Thiên phú đại sư Ⅰ</t>
   </si>
   <si>
-    <t xml:space="preserve">Tính gộp lại thu hoạch được một Thiên phú đỏ</t>
+    <t xml:space="preserve">Tích luỹ nhận được một Thiên phú đỏ</t>
   </si>
   <si>
     <t xml:space="preserve">Thiên phú đại sư Ⅱ</t>
   </si>
   <si>
-    <t xml:space="preserve">Tính gộp lại thu hoạch được năm Thiên phú đỏ</t>
+    <t xml:space="preserve">Tích luỹ nhận được năm Thiên phú đỏ</t>
   </si>
   <si>
     <t xml:space="preserve">Thiên phú đại sư Ⅲ</t>
   </si>
   <si>
-    <t xml:space="preserve">Tính gộp lại thu hoạch được mười Thiên phú đỏ</t>
+    <t xml:space="preserve">Tích luỹ nhận được mười Thiên phú đỏ</t>
   </si>
   <si>
     <t xml:space="preserve">Nội dung chính tuyến</t>
@@ -1438,10 +1438,10 @@
     <t xml:space="preserve">Thông quan chủ tuyến thứ 10 Quan</t>
   </si>
   <si>
-    <t xml:space="preserve">Anh hùng thăng cấp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 Anh hùng đạt tới 30 Cấp</t>
+    <t xml:space="preserve">Tướng thăng cấp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 Tướng đạt tới 30 Cấp</t>
   </si>
   <si>
     <t xml:space="preserve">Cao cấp triệu hoán 1 Lần</t>
@@ -1471,7 +1471,7 @@
     <t xml:space="preserve">Thông quan chủ tuyến thứ 30 Quan</t>
   </si>
   <si>
-    <t xml:space="preserve">Nhân vật chính đẳng cấp đạt tới 18 Cấp</t>
+    <t xml:space="preserve">Nhân vật chính cấp đạt tới 18 Cấp</t>
   </si>
   <si>
     <t xml:space="preserve">Thông quan thông thiên tháp 10 Tầng</t>
@@ -1486,16 +1486,16 @@
     <t xml:space="preserve">Thông quan chủ tuyến thứ 40 Quan</t>
   </si>
   <si>
-    <t xml:space="preserve">Nhân vật chính đẳng cấp đạt tới 25 Cấp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sức chiến đấu cao nhất đạt tới 5 Vạn</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Anh hùng hợp thành</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hợp thành một 5 sao anh hùng</t>
+    <t xml:space="preserve">Nhân vật chính cấp đạt tới 25 Cấp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sức chiến đấu cao nhất đạt tới 50K</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tướng hợp thành</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hợp thành một 5 sao tướng</t>
   </si>
   <si>
     <t xml:space="preserve">Đặc quyền cửa hàng</t>
@@ -1504,10 +1504,10 @@
     <t xml:space="preserve">Mở ra đặc quyền cửa hàng</t>
   </si>
   <si>
-    <t xml:space="preserve">Nhận lấy 5 sao toái phiến</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nhận lấy 5 sao anh hùng mảnh vỡ</t>
+    <t xml:space="preserve">Nhận 5 sao toái phiến</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nhận 5 sao tướng mảnh</t>
   </si>
   <si>
     <t xml:space="preserve">Đạo cụ cửa hàng</t>
@@ -1651,37 +1651,37 @@
     <t xml:space="preserve">Thông quan chủ tuyến thứ 5 Quan</t>
   </si>
   <si>
-    <t xml:space="preserve">Liên tuyến anh hùng</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thông quan liên tuyến anh hùng thứ 1 Quan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thông quan liên tuyến anh hùng thứ 2 Quan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thông quan liên tuyến anh hùng thứ 3 Quan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thông quan liên tuyến anh hùng thứ 4 Quan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thông quan liên tuyến anh hùng thứ 5 Quan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thông quan liên tuyến anh hùng thứ 6 Quan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thông quan liên tuyến anh hùng thứ 7 Quan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thông quan liên tuyến anh hùng thứ 8 Quan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thông quan liên tuyến anh hùng thứ 9 Quan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thông quan liên tuyến anh hùng thứ 10 Quan</t>
+    <t xml:space="preserve">Liên tuyến tướng</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thông quan liên tuyến tướng thứ 1 Quan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thông quan liên tuyến tướng thứ 2 Quan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thông quan liên tuyến tướng thứ 3 Quan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thông quan liên tuyến tướng thứ 4 Quan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thông quan liên tuyến tướng thứ 5 Quan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thông quan liên tuyến tướng thứ 6 Quan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thông quan liên tuyến tướng thứ 7 Quan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thông quan liên tuyến tướng thứ 8 Quan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thông quan liên tuyến tướng thứ 9 Quan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thông quan liên tuyến tướng thứ 10 Quan</t>
   </si>
   <si>
     <t xml:space="preserve">Kích hoạt thần binh 1</t>
@@ -1714,28 +1714,28 @@
     <t xml:space="preserve">Kích hoạt thần binh Red force</t>
   </si>
   <si>
-    <t xml:space="preserve">1 Anh hùng đạt tới 10 Cấp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 Anh hùng đạt tới 30 Cấp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 Anh hùng đạt tới 40 Cấp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 Anh hùng đạt tới 40 Cấp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 Anh hùng đạt tới 50 Cấp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 Anh hùng đạt tới 50 Cấp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 Anh hùng đạt tới 60 Cấp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 Anh hùng đạt tới 60 Cấp</t>
+    <t xml:space="preserve">1 Tướng đạt tới 10 Cấp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 Tướng đạt tới 30 Cấp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 Tướng đạt tới 40 Cấp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 Tướng đạt tới 40 Cấp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 Tướng đạt tới 50 Cấp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 Tướng đạt tới 50 Cấp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 Tướng đạt tới 60 Cấp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 Tướng đạt tới 60 Cấp</t>
   </si>
   <si>
     <t xml:space="preserve">Mặc trang bị</t>
@@ -1744,28 +1744,28 @@
     <t xml:space="preserve">Mặc 1 Lần trang bị</t>
   </si>
   <si>
-    <t xml:space="preserve">Hợp thành một 3 Tinh anh hùng</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hợp thành một 4 Tinh anh hùng</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Anh hùng thu hoạch được</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hợp thành / Thu hoạch được một 5 sao anh hùng</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Anh hùng thăng tinh</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trước mắt có được 2 Cái 4 Tinh anh hùng</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trước mắt có được 2 Cái 5 sao anh hùng</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trước mắt có được một 6 sao anh hùng</t>
+    <t xml:space="preserve">Hợp thành một 3 Tinh tướng</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hợp thành một 4 Tinh tướng</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tướng nhận được</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hợp thành / Nhận được một 5 sao tướng</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tướng thăng tinh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trước mắt có được 2 Cái 4 Tinh tướng</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trước mắt có được 2 Cái 5 sao tướng</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trước mắt có được một 6 sao tướng</t>
   </si>
   <si>
     <t xml:space="preserve">Khiêu chiến kim tệ phó bản</t>
@@ -1813,10 +1813,10 @@
     <t xml:space="preserve">Tàng bảo các bên trong hối đoái 1 Lần</t>
   </si>
   <si>
-    <t xml:space="preserve">Thông quan ban thưởng</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nhận lấy một lần thông quan ban thưởng</t>
+    <t xml:space="preserve">Thông quan thưởng</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nhận một lần thông quan thưởng</t>
   </si>
   <si>
     <t xml:space="preserve">3:100021:1</t>
@@ -1825,7 +1825,7 @@
     <t xml:space="preserve">Ra trận</t>
   </si>
   <si>
-    <t xml:space="preserve">Ra trận một cái mới anh hùng</t>
+    <t xml:space="preserve">Ra trận một cái mới tướng</t>
   </si>
   <si>
     <t xml:space="preserve">Hạn lúc hoạt động - Bò tháp khiêu chiến</t>
@@ -1963,37 +1963,37 @@
     <t xml:space="preserve">Hạn lúc hoạt động - Thăng tinh hào lễ</t>
   </si>
   <si>
-    <t xml:space="preserve">Thăng cấp tùy ý anh hùng đến 6 sao</t>
+    <t xml:space="preserve">Thăng cấp tùy ý tướng đến 6 sao</t>
   </si>
   <si>
     <t xml:space="preserve">5:3:1#3:100004:500#3:100029:10#0:1:1000</t>
   </si>
   <si>
-    <t xml:space="preserve">Thăng cấp tùy ý anh hùng đến 7 sao</t>
+    <t xml:space="preserve">Thăng cấp tùy ý tướng đến 7 sao</t>
   </si>
   <si>
     <t xml:space="preserve">3:100001:1000#3:100029:10#0:1:1000</t>
   </si>
   <si>
-    <t xml:space="preserve">Thăng cấp tùy ý anh hùng đến 8 sao</t>
+    <t xml:space="preserve">Thăng cấp tùy ý tướng đến 8 sao</t>
   </si>
   <si>
     <t xml:space="preserve">0:4:5000000#0:0:5000000#3:100029:10#0:1:1000</t>
   </si>
   <si>
-    <t xml:space="preserve">Thăng cấp tùy ý anh hùng đến 9 sao</t>
+    <t xml:space="preserve">Thăng cấp tùy ý tướng đến 9 sao</t>
   </si>
   <si>
     <t xml:space="preserve">2:19000111:1#2:19000211:1#2:19000311:1#2:19000411:1</t>
   </si>
   <si>
-    <t xml:space="preserve">Thăng cấp tùy ý anh hùng đến 10 sao</t>
+    <t xml:space="preserve">Thăng cấp tùy ý tướng đến 10 sao</t>
   </si>
   <si>
     <t xml:space="preserve">5:4:1#3:100029:10#0:1:1000</t>
   </si>
   <si>
-    <t xml:space="preserve">Nhận lấy một lần thành tựu ban thưởng</t>
+    <t xml:space="preserve">Nhận một lần thành tựu thưởng</t>
   </si>
   <si>
     <t xml:space="preserve">Cây bồ đề tưới nước 1 Lần</t>
@@ -2005,10 +2005,10 @@
     <t xml:space="preserve">3:100022:10</t>
   </si>
   <si>
-    <t xml:space="preserve">Anh hùng thăng giai</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Anh hùng tiến giai</t>
+    <t xml:space="preserve">Tướng thăng giai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tướng tiến giai</t>
   </si>
   <si>
     <t xml:space="preserve">Thăng cấp Hằng Nga đến 6 sao</t>
@@ -2071,19 +2071,19 @@
     <t xml:space="preserve">0:1:2000#3:100025:1</t>
   </si>
   <si>
-    <t xml:space="preserve">Sức chiến đấu cao nhất đạt tới 25 Vạn</t>
+    <t xml:space="preserve">Sức chiến đấu cao nhất đạt tới 250K</t>
   </si>
   <si>
     <t xml:space="preserve">0:1:3000#3:100004:1000</t>
   </si>
   <si>
-    <t xml:space="preserve">Sức chiến đấu cao nhất đạt tới 30 Vạn</t>
+    <t xml:space="preserve">Sức chiến đấu cao nhất đạt tới 300K</t>
   </si>
   <si>
     <t xml:space="preserve">0:1:4000#3:100024:500</t>
   </si>
   <si>
-    <t xml:space="preserve">Sức chiến đấu cao nhất đạt tới 35 Vạn</t>
+    <t xml:space="preserve">Sức chiến đấu cao nhất đạt tới 350K</t>
   </si>
   <si>
     <t xml:space="preserve">0:1:5000#4:603016:50</t>
@@ -2173,13 +2173,13 @@
     <t xml:space="preserve">0:0:100000#5:3:1</t>
   </si>
   <si>
-    <t xml:space="preserve">Tiến hành 10 Lần anh hùng triệu hoán</t>
+    <t xml:space="preserve">Tiến hành 10 Lần tướng triệu hoán</t>
   </si>
   <si>
     <t xml:space="preserve">0:0:20000#3:100001:50</t>
   </si>
   <si>
-    <t xml:space="preserve">Tiến hành 20 Lần anh hùng triệu hoán</t>
+    <t xml:space="preserve">Tiến hành 20 Lần tướng triệu hoán</t>
   </si>
   <si>
     <t xml:space="preserve">0:0:30000#3:100004:80</t>
@@ -2233,34 +2233,34 @@
     <t xml:space="preserve">0:0:100000#3:100005:2</t>
   </si>
   <si>
-    <t xml:space="preserve">Thu hoạch được một 5 sao anh hùng</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thu hoạch được 2 Cái 5 sao anh hùng</t>
+    <t xml:space="preserve">Nhận được một 5 sao tướng</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nhận được 2 Cái 5 sao tướng</t>
   </si>
   <si>
     <t xml:space="preserve">0:0:30000#3:100027:3</t>
   </si>
   <si>
-    <t xml:space="preserve">Thu hoạch được ba 5 sao anh hùng</t>
+    <t xml:space="preserve">Nhận được ba 5 sao tướng</t>
   </si>
   <si>
     <t xml:space="preserve">0:0:50000#3:100027:4</t>
   </si>
   <si>
-    <t xml:space="preserve">Thu hoạch được 4 Cái 5 sao anh hùng</t>
+    <t xml:space="preserve">Nhận được 4 Cái 5 sao tướng</t>
   </si>
   <si>
     <t xml:space="preserve">0:0:80000#3:100027:5</t>
   </si>
   <si>
-    <t xml:space="preserve">Thu hoạch được một 6 sao anh hùng</t>
+    <t xml:space="preserve">Nhận được một 6 sao tướng</t>
   </si>
   <si>
     <t xml:space="preserve">0:0:100000#3:100027:6</t>
   </si>
   <si>
-    <t xml:space="preserve">Thu hoạch được 2 Cái 6 sao anh hùng</t>
+    <t xml:space="preserve">Nhận được 2 Cái 6 sao tướng</t>
   </si>
   <si>
     <t xml:space="preserve">0:0:100000#3:100027:8</t>
@@ -2278,7 +2278,7 @@
     <t xml:space="preserve">Xác nhận 40 lần thưởng thiện phạt ác</t>
   </si>
   <si>
-    <t xml:space="preserve">Tính gộp lại xác nhận 5 Lần tử sắc phẩm chất nhiệm vụ</t>
+    <t xml:space="preserve">Tích luỹ xác nhận 5 Lần tử sắc phẩm chất nhiệm vụ</t>
   </si>
   <si>
     <t xml:space="preserve">Đổi mới 5 Lần thưởng thiện phạt ác</t>
@@ -2320,25 +2320,25 @@
     <t xml:space="preserve">Kích hoạt Hạo Thiên Chùy</t>
   </si>
   <si>
-    <t xml:space="preserve">Đẳng cấp thần binh đạt tới 2 Cấp</t>
+    <t xml:space="preserve">Cấp thần binh đạt tới 2 Cấp</t>
   </si>
   <si>
     <t xml:space="preserve">0:0:50000#3:100002:15</t>
   </si>
   <si>
-    <t xml:space="preserve">Đẳng cấp thần binh đạt tới 3 Cấp</t>
+    <t xml:space="preserve">Cấp thần binh đạt tới 3 Cấp</t>
   </si>
   <si>
     <t xml:space="preserve">0:0:80000#3:100002:15</t>
   </si>
   <si>
-    <t xml:space="preserve">Đẳng cấp thần binh đạt tới 4 Cấp</t>
+    <t xml:space="preserve">Cấp thần binh đạt tới 4 Cấp</t>
   </si>
   <si>
     <t xml:space="preserve">0:0:100000#4:606001:50</t>
   </si>
   <si>
-    <t xml:space="preserve">Đẳng cấp thần binh đạt tới 5 Cấp</t>
+    <t xml:space="preserve">Cấp thần binh đạt tới 5 Cấp</t>
   </si>
   <si>
     <t xml:space="preserve">0:0:20000#4:606001:5</t>
@@ -2353,13 +2353,13 @@
     <t xml:space="preserve">0:0:80000#4:606001:10</t>
   </si>
   <si>
-    <t xml:space="preserve">Nhân vật chính đẳng cấp đạt tới 45 Cấp</t>
+    <t xml:space="preserve">Nhân vật chính cấp đạt tới 45 Cấp</t>
   </si>
   <si>
     <t xml:space="preserve">0:0:100000#4:606001:15</t>
   </si>
   <si>
-    <t xml:space="preserve">Nhân vật chính đẳng cấp đạt tới 55 Cấp</t>
+    <t xml:space="preserve">Nhân vật chính cấp đạt tới 55 Cấp</t>
   </si>
   <si>
     <t xml:space="preserve">Viêm Đế Thí Luyện đạt cao nhất 10 Quan</t>
@@ -2392,7 +2392,7 @@
     <t xml:space="preserve">0:0:100000#3:100005:3</t>
   </si>
   <si>
-    <t xml:space="preserve">Viêm Đế Thí Luyện phái ra 1 Lần anh hùng</t>
+    <t xml:space="preserve">Viêm Đế Thí Luyện phái ra 1 Lần tướng</t>
   </si>
   <si>
     <t xml:space="preserve">Tiến hành 5 Lần may mắn tầm bảo</t>
@@ -2461,13 +2461,13 @@
     <t xml:space="preserve">Đấu trường chiến thắng 20 Lần</t>
   </si>
   <si>
-    <t xml:space="preserve">Trước mắt có được năm 30 Cấp anh hùng</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trước mắt có được một 100 Cấp anh hùng</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trước mắt có được một 120 Cấp anh hùng</t>
+    <t xml:space="preserve">Trước mắt có được năm 30 Cấp tướng</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trước mắt có được một 100 Cấp tướng</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trước mắt có được một 120 Cấp tướng</t>
   </si>
   <si>
     <t xml:space="preserve">0:0:50000#3:100024:10</t>
@@ -2476,7 +2476,7 @@
     <t xml:space="preserve">0:0:80000#4:606001:5</t>
   </si>
   <si>
-    <t xml:space="preserve">Trước mắt có được 2 Cái 6 sao anh hùng</t>
+    <t xml:space="preserve">Trước mắt có được 2 Cái 6 sao tướng</t>
   </si>
   <si>
     <t xml:space="preserve">Đưa tặng hảo hữu hữu nghị điểm 1 Lần</t>
@@ -3157,7 +3157,7 @@
     <t xml:space="preserve">Thổ hào chứng minh</t>
   </si>
   <si>
-    <t xml:space="preserve">Thu hoạch được 500 Nguyên bảo</t>
+    <t xml:space="preserve">Nhận được 500 Nguyên bảo</t>
   </si>
   <si>
     <t xml:space="preserve">Cường giả lịch luyện</t>
@@ -3181,7 +3181,7 @@
     <t xml:space="preserve">Thường ngày sinh động</t>
   </si>
   <si>
-    <t xml:space="preserve">Sinh động độ tính gộp lại đạt tới 100</t>
+    <t xml:space="preserve">Sinh động độ tích luỹ đạt tới 100</t>
   </si>
   <si>
     <t xml:space="preserve">Nữ thần may mắn chiếu cố</t>
@@ -3190,7 +3190,7 @@
     <t xml:space="preserve">3:100208:230</t>
   </si>
   <si>
-    <t xml:space="preserve">Anh hùng chính là lực lượng</t>
+    <t xml:space="preserve">Tướng chính là lực lượng</t>
   </si>
   <si>
     <t xml:space="preserve">Cao cấp triệu hoán 30 Lần</t>
@@ -3208,7 +3208,7 @@
     <t xml:space="preserve">Nhanh chóng đại tác chiến</t>
   </si>
   <si>
-    <t xml:space="preserve">Tính gộp lại nhanh chóng tác chiến 21 Lần</t>
+    <t xml:space="preserve">Tích luỹ nhanh chóng tác chiến 21 Lần</t>
   </si>
   <si>
     <t xml:space="preserve">Treo thưởng đạt nhân</t>
@@ -3220,67 +3220,67 @@
     <t xml:space="preserve">Ngọc cầu nguyện 30 Lần</t>
   </si>
   <si>
-    <t xml:space="preserve">Tùy ý nạp tiền</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nạp tiền tùy ý</t>
+    <t xml:space="preserve">Tùy ý nạp tiền</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nạp tiền tùy ý</t>
   </si>
   <si>
     <t xml:space="preserve">3:100208:250</t>
   </si>
   <si>
-    <t xml:space="preserve">Sửa đá thành vàng</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tính gộp lại đổi tiền xu 10 Lần</t>
+    <t xml:space="preserve">Sửa đá thành vàng</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tích luỹ đổi tiền xu 10 Lần</t>
   </si>
   <si>
     <t xml:space="preserve">4:602021:5#3:100005:1#0:4:50000#3:100029:10#0:1:1000</t>
   </si>
   <si>
-    <t xml:space="preserve">Tính gộp lại đổi tiền xu 20 Lần</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tính gộp lại đổi tiền xu 30 Lần</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tính gộp lại đổi tiền xu 40 Lần</t>
+    <t xml:space="preserve">Tích luỹ đổi tiền xu 20 Lần</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tích luỹ đổi tiền xu 30 Lần</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tích luỹ đổi tiền xu 40 Lần</t>
   </si>
   <si>
     <t xml:space="preserve">4:602021:5#3:100005:2#0:4:100000#3:100029:10#0:1:1000</t>
   </si>
   <si>
-    <t xml:space="preserve">Tính gộp lại đổi tiền xu 50 Lần</t>
+    <t xml:space="preserve">Tích luỹ đổi tiền xu 50 Lần</t>
   </si>
   <si>
     <t xml:space="preserve">4:602021:5#3:100005:3#0:4:100000#3:100029:10#0:1:1000</t>
   </si>
   <si>
-    <t xml:space="preserve">Tính gộp lại đổi tiền xu 60 Lần</t>
+    <t xml:space="preserve">Tích luỹ đổi tiền xu 60 Lần</t>
   </si>
   <si>
     <t xml:space="preserve">4:602021:5#3:100005:4#0:4:100000#3:100029:10#0:1:1000</t>
   </si>
   <si>
-    <t xml:space="preserve">Tính gộp lại đổi tiền xu 70 Lần</t>
+    <t xml:space="preserve">Tích luỹ đổi tiền xu 70 Lần</t>
   </si>
   <si>
     <t xml:space="preserve">4:602021:5#3:100005:5#0:4:150000#3:100029:10#0:1:1000</t>
   </si>
   <si>
-    <t xml:space="preserve">Tính gộp lại đổi tiền xu 80 Lần</t>
+    <t xml:space="preserve">Tích luỹ đổi tiền xu 80 Lần</t>
   </si>
   <si>
     <t xml:space="preserve">4:602021:5#3:100005:6#0:4:150000#3:100029:10#0:1:1000</t>
   </si>
   <si>
-    <t xml:space="preserve">Tính gộp lại đổi tiền xu 90 Lần</t>
+    <t xml:space="preserve">Tích luỹ đổi tiền xu 90 Lần</t>
   </si>
   <si>
     <t xml:space="preserve">4:602021:5#3:100005:6#0:4:200000#3:100029:10#0:1:1000</t>
   </si>
   <si>
-    <t xml:space="preserve">Tính gộp lại đổi tiền xu 100 Lần</t>
+    <t xml:space="preserve">Tích luỹ đổi tiền xu 100 Lần</t>
   </si>
   <si>
     <t xml:space="preserve">vào quán rượu chiêu mộ 1 Lần</t>
@@ -3301,7 +3301,7 @@
     <t xml:space="preserve">Bản phục tam giới tranh bá cạnh đoán 4 Lần</t>
   </si>
   <si>
-    <t xml:space="preserve">Thăng cấp đẳng cấp thần binh 1 Lần</t>
+    <t xml:space="preserve">Thăng cấp cấp thần binh 1 Lần</t>
   </si>
   <si>
     <t xml:space="preserve">Thiên phú đúc lại 1 Lần</t>
@@ -3319,7 +3319,7 @@
     <t xml:space="preserve">Chia sẻ trò chơi 3 Lần</t>
   </si>
   <si>
-    <t xml:space="preserve">Đánh dấu tính gộp lại 5 Lần</t>
+    <t xml:space="preserve">Đánh dấu tích luỹ 5 Lần</t>
   </si>
   <si>
     <t xml:space="preserve">Điểm danh 5 Lần</t>
@@ -3331,61 +3331,61 @@
     <t xml:space="preserve">Hạn lúc hoạt động - Ngọc cầu nguyện</t>
   </si>
   <si>
-    <t xml:space="preserve">Tính gộp lại tùy ý rút hồn ngọc 10 Lần</t>
+    <t xml:space="preserve">Tích luỹ tùy ý rút hồn ngọc 10 Lần</t>
   </si>
   <si>
     <t xml:space="preserve">4:601014:5#3:100005:1#0:4:50000#3:100029:10#0:1:1000</t>
   </si>
   <si>
-    <t xml:space="preserve">Tính gộp lại tùy ý rút hồn ngọc 20 Lần</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tính gộp lại tùy ý rút hồn ngọc 30 Lần</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tính gộp lại tùy ý rút hồn ngọc 40 Lần</t>
+    <t xml:space="preserve">Tích luỹ tùy ý rút hồn ngọc 20 Lần</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tích luỹ tùy ý rút hồn ngọc 30 Lần</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tích luỹ tùy ý rút hồn ngọc 40 Lần</t>
   </si>
   <si>
     <t xml:space="preserve">4:601014:5#3:100005:2#0:4:100000#3:100029:10#0:1:1000</t>
   </si>
   <si>
-    <t xml:space="preserve">Tính gộp lại tùy ý rút hồn ngọc 50 Lần</t>
+    <t xml:space="preserve">Tích luỹ tùy ý rút hồn ngọc 50 Lần</t>
   </si>
   <si>
     <t xml:space="preserve">4:601014:5#3:100005:3#0:4:100000#3:100029:10#0:1:1000</t>
   </si>
   <si>
-    <t xml:space="preserve">Tính gộp lại tùy ý rút hồn ngọc 60 Lần</t>
+    <t xml:space="preserve">Tích luỹ tùy ý rút hồn ngọc 60 Lần</t>
   </si>
   <si>
     <t xml:space="preserve">4:601014:5#3:100005:4#0:4:100000#3:100029:10#0:1:1000</t>
   </si>
   <si>
-    <t xml:space="preserve">Tính gộp lại tùy ý rút hồn ngọc 70 Lần</t>
+    <t xml:space="preserve">Tích luỹ tùy ý rút hồn ngọc 70 Lần</t>
   </si>
   <si>
     <t xml:space="preserve">4:601014:5#3:100005:5#0:4:150000#3:100029:10#0:1:1000</t>
   </si>
   <si>
-    <t xml:space="preserve">Tính gộp lại tùy ý rút hồn ngọc 80 Lần</t>
+    <t xml:space="preserve">Tích luỹ tùy ý rút hồn ngọc 80 Lần</t>
   </si>
   <si>
     <t xml:space="preserve">4:601014:5#3:100005:6#0:4:150000#3:100029:10#0:1:1000</t>
   </si>
   <si>
-    <t xml:space="preserve">Tính gộp lại tùy ý rút hồn ngọc 90 Lần</t>
+    <t xml:space="preserve">Tích luỹ tùy ý rút hồn ngọc 90 Lần</t>
   </si>
   <si>
     <t xml:space="preserve">4:601014:5#3:100005:7#0:4:200000#3:100029:10#0:1:1000</t>
   </si>
   <si>
-    <t xml:space="preserve">Tính gộp lại tùy ý rút hồn ngọc 100 Lần</t>
+    <t xml:space="preserve">Tích luỹ tùy ý rút hồn ngọc 100 Lần</t>
   </si>
   <si>
     <t xml:space="preserve">4:601014:5#3:100005:8#0:4:200000#3:100029:10#0:1:1000</t>
   </si>
   <si>
-    <t xml:space="preserve">Thăng cấp tùy ý anh hùng đến 11 sao</t>
+    <t xml:space="preserve">Thăng cấp tùy ý tướng đến 11 sao</t>
   </si>
   <si>
     <t xml:space="preserve">3:400015:1#3:100046:1#3:100029:10#0:1:1000</t>
@@ -3397,7 +3397,7 @@
     <t xml:space="preserve">0:4:3000000#0:0:3000000#3:100029:10#0:1:1000</t>
   </si>
   <si>
-    <t xml:space="preserve">Thăng cấp tùy ý anh hùng đến 10 sao trở lên</t>
+    <t xml:space="preserve">Thăng cấp tùy ý tướng đến 10 sao trở lên</t>
   </si>
   <si>
     <t xml:space="preserve">5:4:1#3:100046:1#3:100029:10#0:1:1000</t>
@@ -4123,7 +4123,7 @@
     <t xml:space="preserve">Tiến hành Ngọc cầu nguyện</t>
   </si>
   <si>
-    <t xml:space="preserve">Thiên phú nhưng hợp thành a</t>
+    <t xml:space="preserve">Thiên phú có thể hợp thành a</t>
   </si>
   <si>
     <t xml:space="preserve">Tiến hành 7 Lần hợp thiên phú</t>
@@ -4378,7 +4378,7 @@
     <t xml:space="preserve">3:100510:1</t>
   </si>
   <si>
-    <t xml:space="preserve">Thu hoạch được 2000 Nguyên bảo</t>
+    <t xml:space="preserve">Nhận được 2000 Nguyên bảo</t>
   </si>
   <si>
     <t xml:space="preserve">Ngọc tẩy luyện 5 Lần</t>
@@ -4477,7 +4477,7 @@
     <t xml:space="preserve">Mới tới</t>
   </si>
   <si>
-    <t xml:space="preserve">Thông quan anh hùng thí luyện chương 1:</t>
+    <t xml:space="preserve">Thông quan tướng thí luyện chương 1:</t>
   </si>
   <si>
     <t xml:space="preserve">3:200064:500</t>
@@ -4486,25 +4486,25 @@
     <t xml:space="preserve">Ta nghĩ ta sẽ chơi</t>
   </si>
   <si>
-    <t xml:space="preserve">Thông quan anh hùng thí luyện Chương 02:</t>
+    <t xml:space="preserve">Thông quan tướng thí luyện Chương 02:</t>
   </si>
   <si>
     <t xml:space="preserve">Đã hiểu rõ tại tâm</t>
   </si>
   <si>
-    <t xml:space="preserve">Thông quan anh hùng thí luyện chương 3:</t>
+    <t xml:space="preserve">Thông quan tướng thí luyện chương 3:</t>
   </si>
   <si>
     <t xml:space="preserve">Lô hỏa thuần thanh</t>
   </si>
   <si>
-    <t xml:space="preserve">Thông quan anh hùng thí luyện Chương 04:</t>
+    <t xml:space="preserve">Thông quan tướng thí luyện Chương 04:</t>
   </si>
   <si>
     <t xml:space="preserve">Không hắn, trăm hay không bằng tay quen</t>
   </si>
   <si>
-    <t xml:space="preserve">Thông quan anh hùng thí luyện Chương 05:</t>
+    <t xml:space="preserve">Thông quan tướng thí luyện Chương 05:</t>
   </si>
   <si>
     <t xml:space="preserve">0:4:20000</t>
@@ -4531,13 +4531,13 @@
     <t xml:space="preserve">3:100044:10</t>
   </si>
   <si>
-    <t xml:space="preserve">Nhân vật chính đẳng cấp đạt tới 110 Cấp</t>
+    <t xml:space="preserve">Nhân vật chính cấp đạt tới 110 Cấp</t>
   </si>
   <si>
     <t xml:space="preserve">3:100025:5</t>
   </si>
   <si>
-    <t xml:space="preserve">Nhân vật chính đẳng cấp đạt tới 130 Cấp</t>
+    <t xml:space="preserve">Nhân vật chính cấp đạt tới 130 Cấp</t>
   </si>
   <si>
     <t xml:space="preserve">3:100006:10</t>
@@ -4546,76 +4546,76 @@
     <t xml:space="preserve">3:100022:20</t>
   </si>
   <si>
-    <t xml:space="preserve">Nhân vật chính đẳng cấp đạt tới 150 Cấp</t>
+    <t xml:space="preserve">Nhân vật chính cấp đạt tới 150 Cấp</t>
   </si>
   <si>
     <t xml:space="preserve">4:606002:50</t>
   </si>
   <si>
-    <t xml:space="preserve">Nhân vật chính đẳng cấp đạt tới 155 Cấp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nhân vật chính đẳng cấp đạt tới 165 Cấp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nhân vật chính đẳng cấp đạt tới 170 Cấp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nhân vật chính đẳng cấp đạt tới 175 Cấp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nhân vật chính đẳng cấp đạt tới 185 Cấp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nhân vật chính đẳng cấp đạt tới 190 Cấp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nhân vật chính đẳng cấp đạt tới 195 Cấp</t>
+    <t xml:space="preserve">Nhân vật chính cấp đạt tới 155 Cấp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nhân vật chính cấp đạt tới 165 Cấp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nhân vật chính cấp đạt tới 170 Cấp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nhân vật chính cấp đạt tới 175 Cấp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nhân vật chính cấp đạt tới 185 Cấp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nhân vật chính cấp đạt tới 190 Cấp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nhân vật chính cấp đạt tới 195 Cấp</t>
   </si>
   <si>
     <t xml:space="preserve">3:500010:1</t>
   </si>
   <si>
-    <t xml:space="preserve">Kích hoạt một 6 sao duyên phận anh hùng</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kích hoạt ba 6 sao duyên phận anh hùng</t>
+    <t xml:space="preserve">Kích hoạt một 6 sao duyên phận tướng</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kích hoạt ba 6 sao duyên phận tướng</t>
   </si>
   <si>
     <t xml:space="preserve">3:100022:6</t>
   </si>
   <si>
-    <t xml:space="preserve">Kích hoạt năm 6 sao duyên phận anh hùng</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thu hoạch được một 8 sao anh hùng</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thu hoạch được ba 8 sao anh hùng</t>
+    <t xml:space="preserve">Kích hoạt năm 6 sao duyên phận tướng</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nhận được một 8 sao tướng</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nhận được ba 8 sao tướng</t>
   </si>
   <si>
     <t xml:space="preserve">3:100001:600</t>
   </si>
   <si>
-    <t xml:space="preserve">Thu hoạch được năm 8 sao anh hùng</t>
+    <t xml:space="preserve">Nhận được năm 8 sao tướng</t>
   </si>
   <si>
     <t xml:space="preserve">3:100001:1000</t>
   </si>
   <si>
-    <t xml:space="preserve">Thu hoạch được 1 trang bị đỏ</t>
+    <t xml:space="preserve">Nhận được 1 trang bị đỏ</t>
   </si>
   <si>
     <t xml:space="preserve">3:100212:10</t>
   </si>
   <si>
-    <t xml:space="preserve">Thu hoạch được 2 trang bị đỏ</t>
+    <t xml:space="preserve">Nhận được 2 trang bị đỏ</t>
   </si>
   <si>
     <t xml:space="preserve">3:100212:20</t>
   </si>
   <si>
-    <t xml:space="preserve">Thu hoạch được 3 trang bị đỏ</t>
+    <t xml:space="preserve">Nhận được 3 trang bị đỏ</t>
   </si>
   <si>
     <t xml:space="preserve">Tiến hành 4 Lần ấn chú trang bị</t>
@@ -4654,43 +4654,43 @@
     <t xml:space="preserve">3:100216:5000</t>
   </si>
   <si>
-    <t xml:space="preserve">Thu hoạch được 1 Kiện thần trang</t>
+    <t xml:space="preserve">Nhận được 1 Kiện thần trang</t>
   </si>
   <si>
     <t xml:space="preserve">3:100305:1000</t>
   </si>
   <si>
-    <t xml:space="preserve">Thu hoạch được 2 Kiện thần trang</t>
+    <t xml:space="preserve">Nhận được 2 Kiện thần trang</t>
   </si>
   <si>
     <t xml:space="preserve">3:100305:2000</t>
   </si>
   <si>
-    <t xml:space="preserve">Thu hoạch được 3 Kiện thần trang</t>
+    <t xml:space="preserve">Nhận được 3 Kiện thần trang</t>
   </si>
   <si>
     <t xml:space="preserve">3:100305:3000</t>
   </si>
   <si>
-    <t xml:space="preserve">Thu hoạch được một Thiên phú đỏ</t>
+    <t xml:space="preserve">Nhận được một Thiên phú đỏ</t>
   </si>
   <si>
     <t xml:space="preserve">3:100004:2000</t>
   </si>
   <si>
-    <t xml:space="preserve">Thu hoạch được ba Thiên phú đỏ</t>
+    <t xml:space="preserve">Nhận được ba Thiên phú đỏ</t>
   </si>
   <si>
     <t xml:space="preserve">3:100004:4000</t>
   </si>
   <si>
-    <t xml:space="preserve">Thu hoạch được năm Thiên phú đỏ</t>
+    <t xml:space="preserve">Nhận được năm Thiên phú đỏ</t>
   </si>
   <si>
     <t xml:space="preserve">3:100004:6000</t>
   </si>
   <si>
-    <t xml:space="preserve">Thu hoạch được một cao cấp thiên phú</t>
+    <t xml:space="preserve">Nhận được một cao cấp thiên phú</t>
   </si>
   <si>
     <t xml:space="preserve">3:500011:1</t>
@@ -4702,19 +4702,19 @@
     <t xml:space="preserve">Mặc năm cao cấp thiên phú</t>
   </si>
   <si>
-    <t xml:space="preserve">Thu hoạch được một Ngọc thiên cấp</t>
+    <t xml:space="preserve">Nhận được một Ngọc thiên cấp</t>
   </si>
   <si>
     <t xml:space="preserve">3:100036:200</t>
   </si>
   <si>
-    <t xml:space="preserve">Thu hoạch được 2 Cái Ngọc thiên cấp</t>
+    <t xml:space="preserve">Nhận được 2 Cái Ngọc thiên cấp</t>
   </si>
   <si>
     <t xml:space="preserve">3:100036:300</t>
   </si>
   <si>
-    <t xml:space="preserve">Thu hoạch được ba Ngọc thiên cấp</t>
+    <t xml:space="preserve">Nhận được ba Ngọc thiên cấp</t>
   </si>
   <si>
     <t xml:space="preserve">3:100036:400</t>
@@ -4756,16 +4756,16 @@
     <t xml:space="preserve">3:100002:150</t>
   </si>
   <si>
-    <t xml:space="preserve">một Thẻ tướng có thể đến 5 Cấp</t>
+    <t xml:space="preserve">một Thẻ tướng có thể đến 5 Cấp</t>
   </si>
   <si>
     <t xml:space="preserve">3:500019:1</t>
   </si>
   <si>
-    <t xml:space="preserve">2 Cái Thẻ tướng có thể đến 5 Cấp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ba Thẻ tướng có thể đến 5 Cấp</t>
+    <t xml:space="preserve">2 Cái Thẻ tướng có thể đến 5 Cấp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ba Thẻ tướng có thể đến 5 Cấp</t>
   </si>
   <si>
     <t xml:space="preserve">Vượt ải chủ tuyến đạt tới thứ 100 Quan</t>
@@ -5056,10 +5056,10 @@
     <t xml:space="preserve">VIP Trong Thương Thành mua tùy ý đạo cụ ( nguyên bảo hoặc trả tiền )10 Lần</t>
   </si>
   <si>
-    <t xml:space="preserve">VIP Đẳng cấp đạt tới 2 Cấp hoặc trở lên</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VIP Đẳng cấp đạt tới 5 Cấp hoặc trở lên</t>
+    <t xml:space="preserve">VIP Cấp đạt tới 2 Cấp hoặc trở lên</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VIP Cấp đạt tới 5 Cấp hoặc trở lên</t>
   </si>
   <si>
     <t xml:space="preserve">0:1:2000</t>
@@ -5371,7 +5371,7 @@
     <t xml:space="preserve">Độ khó khiêu chiến 5 Vòng</t>
   </si>
   <si>
-    <t xml:space="preserve">Mỗi ngày đánh bại tùy ý màu đỏ năm thú 5 Chỉ</t>
+    <t xml:space="preserve">Mỗi ngày đánh bại tùy ý màu đỏ năm thú 5 Chỉ</t>
   </si>
   <si>
     <t xml:space="preserve">Thường ngày tiêu phí 1 Vòng</t>
@@ -5413,31 +5413,31 @@
     <t xml:space="preserve">Kẹo mềm tiệc tùng 1 Vòng</t>
   </si>
   <si>
-    <t xml:space="preserve">Mỗi ngày đổi mới năm thú số lần đạt tới 10 Lần</t>
+    <t xml:space="preserve">Mỗi ngày đổi mới năm thú lượt đạt tới 10 Lần</t>
   </si>
   <si>
     <t xml:space="preserve">Kẹo mềm tiệc tùng 2 Vòng</t>
   </si>
   <si>
-    <t xml:space="preserve">Mỗi ngày đổi mới năm thú số lần đạt tới 30 Lần</t>
+    <t xml:space="preserve">Mỗi ngày đổi mới năm thú lượt đạt tới 30 Lần</t>
   </si>
   <si>
     <t xml:space="preserve">Kẹo mềm tiệc tùng 3 Vòng</t>
   </si>
   <si>
-    <t xml:space="preserve">Mỗi ngày đổi mới năm thú số lần đạt tới 50 Lần</t>
+    <t xml:space="preserve">Mỗi ngày đổi mới năm thú lượt đạt tới 50 Lần</t>
   </si>
   <si>
     <t xml:space="preserve">Kẹo mềm tiệc tùng 4 Vòng</t>
   </si>
   <si>
-    <t xml:space="preserve">Mỗi ngày đổi mới năm thú số lần đạt tới 100 Lần</t>
+    <t xml:space="preserve">Mỗi ngày đổi mới năm thú lượt đạt tới 100 Lần</t>
   </si>
   <si>
     <t xml:space="preserve">Kẹo mềm tiệc tùng 5 Vòng</t>
   </si>
   <si>
-    <t xml:space="preserve">Mỗi ngày đổi mới năm thú số lần đạt tới 200 Lần</t>
+    <t xml:space="preserve">Mỗi ngày đổi mới năm thú lượt đạt tới 200 Lần</t>
   </si>
   <si>
     <t xml:space="preserve">0:1:4000</t>
@@ -5572,43 +5572,43 @@
     <t xml:space="preserve">4:601023:50#0:0:150000#4:606002:20#3:100029:10#0:1:1000</t>
   </si>
   <si>
-    <t xml:space="preserve">Hạn lúc hoạt động - Anh hùng hiến tế</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Anh hùng hiến tế 10 Lần</t>
+    <t xml:space="preserve">Hạn lúc hoạt động - Tướng hiến tế</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tướng hiến tế 10 Lần</t>
   </si>
   <si>
     <t xml:space="preserve">0:1:50#3:100284:2#3:100029:10#0:1:1000</t>
   </si>
   <si>
-    <t xml:space="preserve">Anh hùng hiến tế 20 Lần</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Anh hùng hiến tế 30 Lần</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Anh hùng hiến tế 40 Lần</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Anh hùng hiến tế 50 Lần</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Anh hùng hiến tế 70 Lần</t>
+    <t xml:space="preserve">Tướng hiến tế 20 Lần</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tướng hiến tế 30 Lần</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tướng hiến tế 40 Lần</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tướng hiến tế 50 Lần</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tướng hiến tế 70 Lần</t>
   </si>
   <si>
     <t xml:space="preserve">0:1:100#3:100284:4#3:400032:1#3:100029:10#0:1:1000</t>
   </si>
   <si>
-    <t xml:space="preserve">Anh hùng hiến tế 90 Lần</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Anh hùng hiến tế 110 Lần</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Anh hùng hiến tế 130 Lần</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Anh hùng hiến tế 150 Lần</t>
+    <t xml:space="preserve">Tướng hiến tế 90 Lần</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tướng hiến tế 110 Lần</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tướng hiến tế 130 Lần</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tướng hiến tế 150 Lần</t>
   </si>
   <si>
     <t xml:space="preserve">Hạn lúc hoạt động - guild đối chiến</t>
@@ -5737,52 +5737,52 @@
     <t xml:space="preserve">3:500011:1#3:100004:3000#3:590008:1#3:100029:10#0:1:1000</t>
   </si>
   <si>
-    <t xml:space="preserve">Hạn lúc hoạt động - Anh hùng tập kết</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thu hoạch được 5 sao anh hùng ba ( Giới hạn mảnh vỡ hợp thành hoặc điểm tướng )</t>
+    <t xml:space="preserve">Hạn lúc hoạt động - Tướng tập kết</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nhận được 5 sao tướng ba ( Giới hạn mảnh hợp thành hoặc điểm tướng )</t>
   </si>
   <si>
     <t xml:space="preserve">0:1:50#4:606008:25#3:100029:10#0:1:1000</t>
   </si>
   <si>
-    <t xml:space="preserve">Thu hoạch được 5 sao anh hùng 6 Cái ( Giới hạn mảnh vỡ hợp thành hoặc điểm tướng )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thu hoạch được 5 sao anh hùng 1năm ( Giới hạn mảnh vỡ hợp thành hoặc điểm tướng )</t>
+    <t xml:space="preserve">Nhận được 5 sao tướng 6 Cái ( Giới hạn mảnh hợp thành hoặc điểm tướng )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nhận được 5 sao tướng 1năm ( Giới hạn mảnh hợp thành hoặc điểm tướng )</t>
   </si>
   <si>
     <t xml:space="preserve">0:1:50#4:606009:25#3:100029:10#0:1:1000</t>
   </si>
   <si>
-    <t xml:space="preserve">Thu hoạch được 5 sao anh hùng 30 Cái ( Giới hạn mảnh vỡ hợp thành hoặc điểm tướng )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thu hoạch được 5 sao anh hùng 50 Cái ( Giới hạn mảnh vỡ hợp thành hoặc điểm tướng )</t>
+    <t xml:space="preserve">Nhận được 5 sao tướng 30 Cái ( Giới hạn mảnh hợp thành hoặc điểm tướng )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nhận được 5 sao tướng 50 Cái ( Giới hạn mảnh hợp thành hoặc điểm tướng )</t>
   </si>
   <si>
     <t xml:space="preserve">0:1:50#4:606010:25#3:100029:10#0:1:1000</t>
   </si>
   <si>
-    <t xml:space="preserve">Thu hoạch được 5 sao anh hùng 70 Cái ( Giới hạn mảnh vỡ hợp thành hoặc điểm tướng )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thu hoạch được 5 sao anh hùng 90 Cái ( Giới hạn mảnh vỡ hợp thành hoặc điểm tướng )</t>
+    <t xml:space="preserve">Nhận được 5 sao tướng 70 Cái ( Giới hạn mảnh hợp thành hoặc điểm tướng )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nhận được 5 sao tướng 90 Cái ( Giới hạn mảnh hợp thành hoặc điểm tướng )</t>
   </si>
   <si>
     <t xml:space="preserve">0:1:50#4:606002:25#4:606015:25#3:100029:10#0:1:1000</t>
   </si>
   <si>
-    <t xml:space="preserve">Thu hoạch được 5 sao anh hùng 120 Cái ( Giới hạn mảnh vỡ hợp thành hoặc điểm tướng )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thu hoạch được 5 sao anh hùng 150 Cái ( Giới hạn mảnh vỡ hợp thành hoặc điểm tướng )</t>
+    <t xml:space="preserve">Nhận được 5 sao tướng 120 Cái ( Giới hạn mảnh hợp thành hoặc điểm tướng )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nhận được 5 sao tướng 150 Cái ( Giới hạn mảnh hợp thành hoặc điểm tướng )</t>
   </si>
   <si>
     <t xml:space="preserve">0:1:50#4:606002:50#4:606015:25#3:100029:10#0:1:1000</t>
   </si>
   <si>
-    <t xml:space="preserve">Thu hoạch được 5 sao anh hùng 180 Cái ( Giới hạn mảnh vỡ hợp thành hoặc điểm tướng )</t>
+    <t xml:space="preserve">Nhận được 5 sao tướng 180 Cái ( Giới hạn mảnh hợp thành hoặc điểm tướng )</t>
   </si>
   <si>
     <t xml:space="preserve">Hạn lúc hoạt động - Đánh lôi đài liên server</t>
@@ -5848,79 +5848,79 @@
     <t xml:space="preserve">重要说明</t>
   </si>
   <si>
-    <t xml:space="preserve">Đăng nhập trò chơi số lần</t>
+    <t xml:space="preserve">Đăng nhập trò chơi lượt</t>
   </si>
   <si>
     <t xml:space="preserve">在实质内容层面：事件类型+参数构成唯一主键，因此，事件类型+参数，要具有唯一性</t>
   </si>
   <si>
-    <t xml:space="preserve">Nhân vật chính mạo hiểm đẳng cấp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ Tính gộp lại ] Đưa tặng hảo hữu hữu nghị điểm số lần</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ Tính gộp lại ] Anh hùng triệu hoán số lần</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ Tính gộp lại ] Hợp thành 6 Tinh anh hùng số lượng</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ Tính gộp lại ] Hợp thành 8 Tinh anh hùng số lượng</t>
-  </si>
-  <si>
-    <t xml:space="preserve">n Anh hùng đạt tới 30 Cấp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">n Anh hùng đạt tới 40 Cấp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">n Anh hùng đạt tới 50 Cấp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">n Anh hùng đạt tới 60 Cấp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">n Anh hùng đạt tới 80 Cấp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">n Anh hùng đạt tới 100 Cấp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">n Anh hùng đạt tới 145 Cấp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">n Anh hùng đạt tới 165 Cấp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">n Anh hùng đạt tới 185 Cấp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">n Anh hùng đạt tới 205 Cấp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">n Anh hùng đạt tới 235 Cấp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Có được n Cái 4 Tinh anh hùng ( Ủng hộ lặp lại anh hùng )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Có được n Cái 5 Tinh anh hùng ( Ủng hộ lặp lại anh hùng )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tính gộp lại thu hoạch được n Cái 6 Tinh anh hùng ( Ủng hộ lặp lại anh hùng )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ Tính gộp lại ] Phổ thông triệu hoán anh hùng số lần</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ Tính gộp lại ] Cao cấp triệu hoán anh hùng số lần</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ Tính gộp lại ] Hiểu số mệnh con người xem đoán xâm số lần</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ Tính gộp lại ] Anh hùng phân giải số lượng</t>
+    <t xml:space="preserve">Nhân vật chính mạo hiểm cấp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[ Tích luỹ ] Đưa tặng hảo hữu hữu nghị điểm lượt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[ Tích luỹ ] Tướng triệu hoán lượt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[ Tích luỹ ] Hợp thành 6 Tinh tướng số lượng</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[ Tích luỹ ] Hợp thành 8 Tinh tướng số lượng</t>
+  </si>
+  <si>
+    <t xml:space="preserve">n Tướng đạt tới 30 Cấp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">n Tướng đạt tới 40 Cấp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">n Tướng đạt tới 50 Cấp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">n Tướng đạt tới 60 Cấp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">n Tướng đạt tới 80 Cấp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">n Tướng đạt tới 100 Cấp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">n Tướng đạt tới 145 Cấp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">n Tướng đạt tới 165 Cấp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">n Tướng đạt tới 185 Cấp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">n Tướng đạt tới 205 Cấp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">n Tướng đạt tới 235 Cấp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Có được n Cái 4 Tinh tướng ( Ủng hộ lặp lại tướng )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Có được n Cái 5 Tinh tướng ( Ủng hộ lặp lại tướng )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tích luỹ nhận được n Cái 6 Tinh tướng ( Ủng hộ lặp lại tướng )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[ Tích luỹ ] Phổ thông triệu hoán tướng lượt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[ Tích luỹ ] Cao cấp triệu hoán tướng lượt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[ Tích luỹ ] Hiểu số mệnh con người xem đoán xâm lượt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[ Tích luỹ ] Tướng phân giải số lượng</t>
   </si>
   <si>
     <t xml:space="preserve">Có được hảo hữu số lượng</t>
@@ -5932,10 +5932,10 @@
     <t xml:space="preserve">Có được n Kiện màu cam phẩm chất trang bị</t>
   </si>
   <si>
-    <t xml:space="preserve">Có được n Kiện màu đỏ phẩm chất trang bị</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tính gộp lại tiến hành n Lần tỉ ấn hợp thành</t>
+    <t xml:space="preserve">Có được n Kiện màu đỏ phẩm chất trang bị</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tích luỹ tiến hành n Lần tỉ ấn hợp thành</t>
   </si>
   <si>
     <t xml:space="preserve">Diễn võ trường điểm tích lũy đạt tới n</t>
@@ -5944,16 +5944,16 @@
     <t xml:space="preserve">Diễn võ trường xếp hạng</t>
   </si>
   <si>
-    <t xml:space="preserve">Khiêu chiến thường ngày phó bản số lần</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ Tính gộp lại ] Xác nhận x Lần tử sắc phẩm chất chạy thương nhiệm vụ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ Tính gộp lại ] Xác nhận x Lần màu cam phẩm chất chạy thương nhiệm vụ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ Tính gộp lại ] Xác nhận x Lần màu đỏ phẩm chất chạy thương nhiệm vụ</t>
+    <t xml:space="preserve">Khiêu chiến thường ngày phó bản lượt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[ Tích luỹ ] Xác nhận x Lần tử sắc phẩm chất chạy thương nhiệm vụ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[ Tích luỹ ] Xác nhận x Lần màu cam phẩm chất chạy thương nhiệm vụ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[ Tích luỹ ] Xác nhận x Lần màu đỏ phẩm chất chạy thương nhiệm vụ</t>
   </si>
   <si>
     <t xml:space="preserve">Côn Luân bí cảnh ( Tùy ý độ khó ) Thắng lợi n Lần</t>
@@ -5962,7 +5962,7 @@
     <t xml:space="preserve">Sáng tạo hoặc gia nhập tiên minh</t>
   </si>
   <si>
-    <t xml:space="preserve">[ Tính gộp lại ] Khiêu chiến n Lần tiên minh phó bản</t>
+    <t xml:space="preserve">[ Tích luỹ ] Khiêu chiến n Lần tiên minh phó bản</t>
   </si>
   <si>
     <t xml:space="preserve">Tại PVP Chiến đấu bên trong, 8 Hiệp nội chiến thắng chiến lực cao hơn đối thủ của mình n Lần</t>
@@ -5974,25 +5974,25 @@
     <t xml:space="preserve">Tại PVP Chiến đấu bên trong, 6 Hiệp nội chiến thắng chiến lực cao hơn đối thủ của mình n Lần</t>
   </si>
   <si>
-    <t xml:space="preserve">Tại PVP Chiến đấu bên trong, chiến thắng chiến lực cao hơn tự thân 10 Vạn đối thủ n Lần</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tại PVP Chiến đấu bên trong, chiến thắng chiến lực cao hơn tự thân 20 Vạn đối thủ n Lần</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tại PVP Chiến đấu bên trong, chiến thắng chiến lực cao hơn tự thân 30 Vạn đối thủ n Lần</t>
+    <t xml:space="preserve">Tại PVP Chiến đấu bên trong, chiến thắng chiến lực cao hơn tự thân 100K đối thủ n Lần</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tại PVP Chiến đấu bên trong, chiến thắng chiến lực cao hơn tự thân 200K đối thủ n Lần</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tại PVP Chiến đấu bên trong, chiến thắng chiến lực cao hơn tự thân 300K đối thủ n Lần</t>
   </si>
   <si>
     <t xml:space="preserve">Tại PVP Chiến đấu bên trong, đầy máu đủ quân số chiến thắng chiến lực cao hơn tự thân đối thủ n Lần</t>
   </si>
   <si>
-    <t xml:space="preserve">Tại PVP Chiến đấu bên trong, sử dụng pháp bảo tính gộp lại đánh giết địch quân anh hùng n Lần</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tại PVP Chiến đấu bên trong, sử dụng 【 Chùy 】 Pháp bảo tính gộp lại mê muội n Cái địch quân anh hùng</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tại đơn trận PVP Chiến đấu bên trong sử dụng kỹ năng chủ động phục sinh phe mình anh hùng n Lần</t>
+    <t xml:space="preserve">Tại PVP Chiến đấu bên trong, sử dụng pháp bảo tích luỹ đánh giết địch quân tướng n Lần</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tại PVP Chiến đấu bên trong, sử dụng 【 Chùy 】 Pháp bảo tích luỹ mê muội n Cái địch quân tướng</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tại đơn trận PVP Chiến đấu bên trong sử dụng kỹ năng chủ động phục sinh phe mình tướng n Lần</t>
   </si>
   <si>
     <t xml:space="preserve">Tại đơn trận PVP Chiến đấu bên trong tổng trị liệu lượng đạt tới n</t>
@@ -6004,55 +6004,55 @@
     <t xml:space="preserve">Tùy ý 1 Loại đồ đằng Thánh Điện lịch sử tối cao thông quan số đạt tới n</t>
   </si>
   <si>
-    <t xml:space="preserve">Tính gộp lại tiến vào đồ đằng Thánh Điện bảng xếp hạng trước 10 Tên n Lần</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tính gộp lại tiến vào đồ đằng Thánh Điện bảng xếp hạng trước 3 Tên n Lần</t>
+    <t xml:space="preserve">Tích luỹ tiến vào đồ đằng Thánh Điện bảng xếp hạng trước 10 Tên n Lần</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tích luỹ tiến vào đồ đằng Thánh Điện bảng xếp hạng trước 3 Tên n Lần</t>
   </si>
   <si>
     <t xml:space="preserve">Nhân vật chính chiến lực</t>
   </si>
   <si>
-    <t xml:space="preserve">Trước mắt có được n Cái khác biệt 10 Tinh anh hùng ( Không hỗ trợ lặp lại anh hùng )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tính gộp lại thu hoạch được n Cái khác biệt 10 Tinh nhân tộc anh hùng ( Không hỗ trợ lặp lại anh hùng )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tính gộp lại thu hoạch được n Cái khác biệt 10 Tinh Tiên Tộc anh hùng ( Không hỗ trợ lặp lại anh hùng )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tính gộp lại thu hoạch được n Cái khác biệt 10 Tinh yêu tộc anh hùng ( Không hỗ trợ lặp lại anh hùng )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tính gộp lại thu hoạch được n Cái khác biệt 10 Tinh Thần tộc anh hùng ( Không hỗ trợ lặp lại anh hùng )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tính gộp lại thu hoạch được n Cái khác biệt 10 Tinh ma tộc anh hùng ( Không hỗ trợ lặp lại anh hùng )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tính gộp lại lĩnh ngộ n Cái sơ cấp thiên phú</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tính gộp lại lĩnh ngộ n Cái trung cấp thiên phú</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tính gộp lại lĩnh ngộ n Cái cao cấp thiên phú</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Đơn cuộc chiến đấu tính gộp lại tạo thành n Điểm trúng độc thương hại</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Đơn cuộc chiến đấu tính gộp lại tạo thành n Điểm thiêu đốt tổn thương</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Đơn cuộc chiến đấu tính gộp lại tạo thành n Điểm chảy máu tổn thương</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Đơn trận tiên minh phó bản chiến đấu bên trong tính gộp lại tạo thành n Điểm thương tổn</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tính gộp lại thu hoạch được n Cái màu đỏ phẩm chất tỉ ấn</t>
+    <t xml:space="preserve">Trước mắt có được n Cái khác biệt 10 Tinh tướng ( Không hỗ trợ lặp lại tướng )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tích luỹ nhận được n Cái khác biệt 10 Tinh nhân tộc tướng ( Không hỗ trợ lặp lại tướng )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tích luỹ nhận được n Cái khác biệt 10 Tinh Tiên Tộc tướng ( Không hỗ trợ lặp lại tướng )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tích luỹ nhận được n Cái khác biệt 10 Tinh yêu tộc tướng ( Không hỗ trợ lặp lại tướng )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tích luỹ nhận được n Cái khác biệt 10 Tinh Thần tộc tướng ( Không hỗ trợ lặp lại tướng )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tích luỹ nhận được n Cái khác biệt 10 Tinh ma tộc tướng ( Không hỗ trợ lặp lại tướng )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tích luỹ lĩnh ngộ n Cái sơ cấp thiên phú</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tích luỹ lĩnh ngộ n Cái trung cấp thiên phú</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tích luỹ lĩnh ngộ n Cái cao cấp thiên phú</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Đơn cuộc chiến đấu tích luỹ tạo thành n Điểm trúng độc thương hại</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Đơn cuộc chiến đấu tích luỹ tạo thành n Điểm thiêu đốt tổn thương</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Đơn cuộc chiến đấu tích luỹ tạo thành n Điểm chảy máu tổn thương</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Đơn trận tiên minh phó bản chiến đấu bên trong tích luỹ tạo thành n Điểm thương tổn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tích luỹ nhận được n Cái màu đỏ phẩm chất tỉ ấn</t>
   </si>
   <si>
     <t xml:space="preserve">Linh Lung Tháp lịch sử tối cao thông quan số đạt tới n</t>
@@ -6082,10 +6082,10 @@
     <t xml:space="preserve">Kích hoạt pháp bảo 5</t>
   </si>
   <si>
-    <t xml:space="preserve">Có được n Cái 9 Tinh anh hùng ( Ủng hộ lặp lại anh hùng )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Có được n Cái 10 Tinh anh hùng ( Ủng hộ lặp lại anh hùng )</t>
+    <t xml:space="preserve">Có được n Cái 9 Tinh tướng ( Ủng hộ lặp lại tướng )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Có được n Cái 10 Tinh tướng ( Ủng hộ lặp lại tướng )</t>
   </si>
   <si>
     <t xml:space="preserve">Đánh giết n Cái tiên minh phó bản</t>
@@ -6106,7 +6106,7 @@
     <t xml:space="preserve">Khiêu chiến 1 Lần Côn Luân bí cảnh</t>
   </si>
   <si>
-    <t xml:space="preserve">Tính gộp lại đánh dấu 2 Trời</t>
+    <t xml:space="preserve">Tích luỹ đánh dấu 2 Trời</t>
   </si>
   <si>
     <t xml:space="preserve">Côn Luân bí cảnh ( Tùy ý độ khó ) Lịch sử tối cao thông quan quan số</t>
@@ -6124,58 +6124,58 @@
     <t xml:space="preserve">Đổi mới n Lần treo thưởng nhiệm vụ</t>
   </si>
   <si>
-    <t xml:space="preserve">Đẳng cấp pháp bảo đạt tới 2 Cấp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Đẳng cấp pháp bảo đạt tới 3 Cấp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Đẳng cấp pháp bảo đạt tới 4 Cấp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Đẳng cấp pháp bảo đạt tới 5 Cấp</t>
+    <t xml:space="preserve">Cấp pháp bảo đạt tới 2 Cấp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cấp pháp bảo đạt tới 3 Cấp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cấp pháp bảo đạt tới 4 Cấp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cấp pháp bảo đạt tới 5 Cấp</t>
   </si>
   <si>
     <t xml:space="preserve">Diễn võ trường chiến thắng n Lần</t>
   </si>
   <si>
-    <t xml:space="preserve">Vô tận luân hồi phái ra 1 Lần anh hùng</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trước mắt có được 1 Cái 99 Cấp anh hùng</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trước mắt có được 1 Cái 120 Cấp anh hùng</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trước mắt có được n Cái 6 Tinh anh hùng</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tính gộp lại thu hoạch được 3 Cái 145 Cấp anh hùng</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tính gộp lại thu hoạch được 5 Cái 165 Cấp anh hùng</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tính gộp lại thu hoạch được 3 Cái 185 Cấp anh hùng</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tính gộp lại thu hoạch được 5 Cái 205 Cấp anh hùng</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tính gộp lại thu hoạch được 3 Cái 255 Cấp anh hùng</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ Tính gộp lại hợp thành 5 Tinh anh hùng số lượng</t>
+    <t xml:space="preserve">Vô tận luân hồi phái ra 1 Lần tướng</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trước mắt có được 1 Cái 99 Cấp tướng</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trước mắt có được 1 Cái 120 Cấp tướng</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trước mắt có được n Cái 6 Tinh tướng</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tích luỹ nhận được 3 Cái 145 Cấp tướng</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tích luỹ nhận được 5 Cái 165 Cấp tướng</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tích luỹ nhận được 3 Cái 185 Cấp tướng</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tích luỹ nhận được 5 Cái 205 Cấp tướng</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tích luỹ nhận được 3 Cái 255 Cấp tướng</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[ Tích luỹ hợp thành 5 Tinh tướng số lượng</t>
   </si>
   <si>
     <t xml:space="preserve">Côn Luân bí cảnh thắng lợi 3 Lần</t>
   </si>
   <si>
-    <t xml:space="preserve">Tính gộp lại thu hoạch được Nguyên bảo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tính gộp lại thú hồn cầu nguyện số lần ( Không chỉ định loại hình )</t>
+    <t xml:space="preserve">Tích luỹ nhận được Nguyên bảo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tích luỹ thú hồn cầu nguyện lượt ( Không chỉ định loại hình )</t>
   </si>
   <si>
     <t xml:space="preserve">Tưới nước</t>
@@ -6184,79 +6184,79 @@
     <t xml:space="preserve">Mặc Thần khí</t>
   </si>
   <si>
-    <t xml:space="preserve">Tính gộp lại thu hoạch được một bộ nhân tộc anh hùng 5 Tinh đồ giám</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tính gộp lại thu hoạch được một bộ Tiên Tộc anh hùng 5 Tinh đồ giám</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tính gộp lại thu hoạch được một bộ yêu tộc anh hùng 5 Tinh đồ giám</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tính gộp lại thu hoạch được một bộ Thần tộc anh hùng 5 Tinh đồ giám</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tính gộp lại thu hoạch được một bộ ma tộc anh hùng 5 Tinh đồ giám</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lần đầu hợp thành thu hoạch được vũ khí đỏ 1 Tinh</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lần đầu hợp thành thu hoạch được vũ khí đỏ 2 Tinh</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lần đầu hợp thành thu hoạch được vũ khí đỏ 3 Tinh</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lần đầu hợp thành thu hoạch được vũ khí đỏ 4 Tinh</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lần đầu hợp thành thu hoạch được vũ khí đỏ 5 Tinh</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lần đầu hợp thành thu hoạch được quần áo đỏ 1 Tinh</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lần đầu hợp thành thu hoạch được quần áo đỏ 2 Tinh</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lần đầu hợp thành thu hoạch được quần áo đỏ 3 Tinh</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lần đầu hợp thành thu hoạch được quần áo đỏ 4 Tinh</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lần đầu hợp thành thu hoạch được quần áo đỏ 5 Tinh</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lần đầu hợp thành thu hoạch được giày đỏ 1 Tinh</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lần đầu hợp thành thu hoạch được giày đỏ 2 Tinh</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lần đầu hợp thành thu hoạch được giày đỏ 3 Tinh</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lần đầu hợp thành thu hoạch được giày đỏ 4 Tinh</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lần đầu hợp thành thu hoạch được giày đỏ 5 Tinh</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lần đầu hợp thành thu hoạch được mũ đỏ 1 Tinh</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lần đầu hợp thành thu hoạch được mũ đỏ 2 Tinh</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lần đầu hợp thành thu hoạch được mũ đỏ 3 Tinh</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lần đầu hợp thành thu hoạch được mũ đỏ 4 Tinh</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lần đầu hợp thành thu hoạch được mũ đỏ 5 Tinh</t>
+    <t xml:space="preserve">Tích luỹ nhận được một bộ nhân tộc tướng 5 Tinh đồ giám</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tích luỹ nhận được một bộ Tiên Tộc tướng 5 Tinh đồ giám</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tích luỹ nhận được một bộ yêu tộc tướng 5 Tinh đồ giám</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tích luỹ nhận được một bộ Thần tộc tướng 5 Tinh đồ giám</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tích luỹ nhận được một bộ ma tộc tướng 5 Tinh đồ giám</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lần đầu hợp thành nhận được vũ khí đỏ 1 Tinh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lần đầu hợp thành nhận được vũ khí đỏ 2 Tinh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lần đầu hợp thành nhận được vũ khí đỏ 3 Tinh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lần đầu hợp thành nhận được vũ khí đỏ 4 Tinh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lần đầu hợp thành nhận được vũ khí đỏ 5 Tinh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lần đầu hợp thành nhận được quần áo đỏ 1 Tinh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lần đầu hợp thành nhận được quần áo đỏ 2 Tinh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lần đầu hợp thành nhận được quần áo đỏ 3 Tinh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lần đầu hợp thành nhận được quần áo đỏ 4 Tinh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lần đầu hợp thành nhận được quần áo đỏ 5 Tinh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lần đầu hợp thành nhận được giày đỏ 1 Tinh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lần đầu hợp thành nhận được giày đỏ 2 Tinh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lần đầu hợp thành nhận được giày đỏ 3 Tinh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lần đầu hợp thành nhận được giày đỏ 4 Tinh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lần đầu hợp thành nhận được giày đỏ 5 Tinh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lần đầu hợp thành nhận được mũ đỏ 1 Tinh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lần đầu hợp thành nhận được mũ đỏ 2 Tinh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lần đầu hợp thành nhận được mũ đỏ 3 Tinh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lần đầu hợp thành nhận được mũ đỏ 4 Tinh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lần đầu hợp thành nhận được mũ đỏ 5 Tinh</t>
   </si>
   <si>
     <t xml:space="preserve">Linh Lung Tháp số tầng 30</t>
@@ -6313,10 +6313,10 @@
     <t xml:space="preserve">Linh Lung Tháp số tầng 400</t>
   </si>
   <si>
-    <t xml:space="preserve">Nhận lấy 5 Tinh anh hùng mảnh vỡ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Liên tuyến anh hùng thông quan chỉ định cửa ải</t>
+    <t xml:space="preserve">Nhận 5 Tinh tướng mảnh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Liên tuyến tướng thông quan chỉ định cửa ải</t>
   </si>
   <si>
     <t xml:space="preserve">任务ID</t>
@@ -6479,6 +6479,9 @@
   </si>
   <si>
     <t xml:space="preserve">Tích nạp 100 Nguyên</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nạp tiền nhiệm vụ</t>
   </si>
   <si>
     <t xml:space="preserve">Tích nạp 200 Nguyên</t>
@@ -58261,10 +58264,10 @@
         <v>4001</v>
       </c>
       <c r="C2" t="s">
-        <v>2149</v>
+        <v>2151</v>
       </c>
       <c r="D2" t="s">
-        <v>2151</v>
+        <v>2152</v>
       </c>
       <c r="G2" t="n">
         <v>200</v>
@@ -58290,10 +58293,10 @@
         <v>4001</v>
       </c>
       <c r="C3" t="s">
-        <v>2149</v>
+        <v>2151</v>
       </c>
       <c r="D3" t="s">
-        <v>2152</v>
+        <v>2153</v>
       </c>
       <c r="G3" t="n">
         <v>500</v>
@@ -58308,7 +58311,7 @@
         <v>2</v>
       </c>
       <c r="R3" t="s">
-        <v>2153</v>
+        <v>2154</v>
       </c>
     </row>
     <row r="4">
@@ -58319,10 +58322,10 @@
         <v>4001</v>
       </c>
       <c r="C4" t="s">
-        <v>2149</v>
+        <v>2151</v>
       </c>
       <c r="D4" t="s">
-        <v>2154</v>
+        <v>2155</v>
       </c>
       <c r="G4" t="n">
         <v>1000</v>
@@ -58348,10 +58351,10 @@
         <v>4001</v>
       </c>
       <c r="C5" t="s">
-        <v>2149</v>
+        <v>2151</v>
       </c>
       <c r="D5" t="s">
-        <v>2155</v>
+        <v>2156</v>
       </c>
       <c r="G5" t="n">
         <v>2000</v>
@@ -58377,10 +58380,10 @@
         <v>4001</v>
       </c>
       <c r="C6" t="s">
-        <v>2149</v>
+        <v>2151</v>
       </c>
       <c r="D6" t="s">
-        <v>2156</v>
+        <v>2157</v>
       </c>
       <c r="G6" t="n">
         <v>3000</v>
@@ -58395,7 +58398,7 @@
         <v>2</v>
       </c>
       <c r="R6" t="s">
-        <v>2157</v>
+        <v>2158</v>
       </c>
     </row>
     <row r="7">
@@ -58406,10 +58409,10 @@
         <v>4001</v>
       </c>
       <c r="C7" t="s">
-        <v>2149</v>
+        <v>2151</v>
       </c>
       <c r="D7" t="s">
-        <v>2158</v>
+        <v>2159</v>
       </c>
       <c r="G7" t="n">
         <v>5000</v>
@@ -58424,7 +58427,7 @@
         <v>2</v>
       </c>
       <c r="R7" t="s">
-        <v>2159</v>
+        <v>2160</v>
       </c>
     </row>
   </sheetData>
@@ -58443,106 +58446,106 @@
   <sheetData>
     <row r="19">
       <c r="G19" t="s">
-        <v>2160</v>
+        <v>2161</v>
       </c>
     </row>
     <row r="20">
       <c r="F20" t="s">
-        <v>2161</v>
+        <v>2162</v>
       </c>
       <c r="G20" t="s">
-        <v>2162</v>
+        <v>2163</v>
       </c>
       <c r="H20" t="s">
-        <v>2162</v>
+        <v>2163</v>
       </c>
     </row>
     <row r="21">
       <c r="F21" t="s">
-        <v>2163</v>
+        <v>2164</v>
       </c>
       <c r="G21" t="s">
-        <v>2164</v>
+        <v>2165</v>
       </c>
       <c r="H21" t="s">
-        <v>2165</v>
+        <v>2166</v>
       </c>
     </row>
     <row r="22">
       <c r="F22" t="s">
-        <v>2166</v>
+        <v>2167</v>
       </c>
       <c r="G22" t="s">
-        <v>2167</v>
+        <v>2168</v>
       </c>
       <c r="H22" t="s">
-        <v>2168</v>
+        <v>2169</v>
       </c>
     </row>
     <row r="23">
       <c r="F23" t="s">
-        <v>2169</v>
+        <v>2170</v>
       </c>
       <c r="G23" t="s">
-        <v>2170</v>
+        <v>2171</v>
       </c>
       <c r="H23" t="s">
-        <v>2171</v>
+        <v>2172</v>
       </c>
     </row>
     <row r="24">
       <c r="F24" t="s">
-        <v>2172</v>
+        <v>2173</v>
       </c>
       <c r="G24" t="s">
-        <v>2173</v>
+        <v>2174</v>
       </c>
       <c r="H24" t="s">
-        <v>2174</v>
+        <v>2175</v>
       </c>
     </row>
     <row r="25">
       <c r="F25" t="s">
-        <v>2175</v>
+        <v>2176</v>
       </c>
       <c r="G25" t="s">
-        <v>2176</v>
+        <v>2177</v>
       </c>
       <c r="H25" t="s">
-        <v>2176</v>
+        <v>2177</v>
       </c>
     </row>
     <row r="26">
       <c r="F26" t="s">
-        <v>2177</v>
+        <v>2178</v>
       </c>
       <c r="G26" t="s">
-        <v>2178</v>
+        <v>2179</v>
       </c>
       <c r="H26" t="s">
-        <v>2179</v>
+        <v>2180</v>
       </c>
     </row>
     <row r="27">
       <c r="F27" t="s">
-        <v>2180</v>
+        <v>2181</v>
       </c>
       <c r="G27" t="s">
-        <v>2181</v>
+        <v>2182</v>
       </c>
       <c r="H27" t="s">
-        <v>2182</v>
+        <v>2183</v>
       </c>
     </row>
     <row r="28">
       <c r="F28" t="s">
-        <v>2183</v>
+        <v>2184</v>
       </c>
       <c r="G28" t="s">
-        <v>2184</v>
+        <v>2185</v>
       </c>
       <c r="H28" t="s">
-        <v>2185</v>
+        <v>2186</v>
       </c>
     </row>
   </sheetData>

--- a/server/excel/release/quest.xlsx
+++ b/server/excel/release/quest.xlsx
@@ -2536,7 +2536,7 @@
     <t xml:space="preserve">Thông quan càn quét thông thiên tháp 1 Lần</t>
   </si>
   <si>
-    <t xml:space="preserve">Tiêu hao 500 Nguyên bảo</t>
+    <t xml:space="preserve">Tiêu hao 500 Kim cương</t>
   </si>
   <si>
     <t xml:space="preserve">Cẩm nang chi mê ngày thứ ba</t>
@@ -3157,7 +3157,7 @@
     <t xml:space="preserve">Thổ hào chứng minh</t>
   </si>
   <si>
-    <t xml:space="preserve">Nhận được 500 Nguyên bảo</t>
+    <t xml:space="preserve">Nhận được 500 Kim cương</t>
   </si>
   <si>
     <t xml:space="preserve">Cường giả lịch luyện</t>
@@ -4369,7 +4369,7 @@
     <t xml:space="preserve">Thường ngày tiêu phí</t>
   </si>
   <si>
-    <t xml:space="preserve">Mỗi ngày tiêu hao nguyên bảo 2000</t>
+    <t xml:space="preserve">Mỗi ngày tiêu hao kim cương 2000</t>
   </si>
   <si>
     <t xml:space="preserve">Mỗi ngày tặng bảo</t>
@@ -4378,7 +4378,7 @@
     <t xml:space="preserve">3:100510:1</t>
   </si>
   <si>
-    <t xml:space="preserve">Nhận được 2000 Nguyên bảo</t>
+    <t xml:space="preserve">Nhận được 2000 Kim cương</t>
   </si>
   <si>
     <t xml:space="preserve">Ngọc tẩy luyện 5 Lần</t>
@@ -5047,13 +5047,13 @@
     <t xml:space="preserve">Tiến hành 50 Lần cao cấp chiêu mộ</t>
   </si>
   <si>
-    <t xml:space="preserve">VIP Trong Thương Thành mua tùy ý đạo cụ ( nguyên bảo hoặc trả tiền )1 Lần</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VIP Trong Thương Thành mua tùy ý đạo cụ ( nguyên bảo hoặc trả tiền )3 Lần</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VIP Trong Thương Thành mua tùy ý đạo cụ ( nguyên bảo hoặc trả tiền )10 Lần</t>
+    <t xml:space="preserve">VIP Trong Thương Thành mua tùy ý đạo cụ ( kim cương hoặc trả tiền )1 Lần</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VIP Trong Thương Thành mua tùy ý đạo cụ ( kim cương hoặc trả tiền )3 Lần</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VIP Trong Thương Thành mua tùy ý đạo cụ ( kim cương hoặc trả tiền )10 Lần</t>
   </si>
   <si>
     <t xml:space="preserve">VIP Cấp đạt tới 2 Cấp hoặc trở lên</t>
@@ -5377,37 +5377,37 @@
     <t xml:space="preserve">Thường ngày tiêu phí 1 Vòng</t>
   </si>
   <si>
-    <t xml:space="preserve">Mỗi ngày tiêu hao 100 Nguyên bảo</t>
+    <t xml:space="preserve">Mỗi ngày tiêu hao 100 Kim cương</t>
   </si>
   <si>
     <t xml:space="preserve">Thường ngày tiêu phí 2 Vòng</t>
   </si>
   <si>
-    <t xml:space="preserve">Mỗi ngày tiêu hao nguyên bảo 600</t>
+    <t xml:space="preserve">Mỗi ngày tiêu hao kim cương 600</t>
   </si>
   <si>
     <t xml:space="preserve">Thường ngày tiêu phí 3 Vòng</t>
   </si>
   <si>
-    <t xml:space="preserve">Mỗi ngày tiêu hao nguyên bảo 1500</t>
+    <t xml:space="preserve">Mỗi ngày tiêu hao kim cương 1500</t>
   </si>
   <si>
     <t xml:space="preserve">Thường ngày tiêu phí 4 Vòng</t>
   </si>
   <si>
-    <t xml:space="preserve">Mỗi ngày tiêu hao nguyên bảo 4000</t>
+    <t xml:space="preserve">Mỗi ngày tiêu hao kim cương 4000</t>
   </si>
   <si>
     <t xml:space="preserve">Thường ngày tiêu phí 5 Vòng</t>
   </si>
   <si>
-    <t xml:space="preserve">Mỗi ngày tiêu hao nguyên bảo 10000</t>
+    <t xml:space="preserve">Mỗi ngày tiêu hao kim cương 10000</t>
   </si>
   <si>
     <t xml:space="preserve">Thường ngày tiêu phí 6 Vòng</t>
   </si>
   <si>
-    <t xml:space="preserve">Mỗi ngày tiêu hao nguyên bảo 20000</t>
+    <t xml:space="preserve">Mỗi ngày tiêu hao kim cương 20000</t>
   </si>
   <si>
     <t xml:space="preserve">Kẹo mềm tiệc tùng 1 Vòng</t>
@@ -6172,7 +6172,7 @@
     <t xml:space="preserve">Côn Luân bí cảnh thắng lợi 3 Lần</t>
   </si>
   <si>
-    <t xml:space="preserve">Tích luỹ nhận được Nguyên bảo</t>
+    <t xml:space="preserve">Tích luỹ nhận được Kim cương</t>
   </si>
   <si>
     <t xml:space="preserve">Tích luỹ thú hồn cầu nguyện lượt ( Không chỉ định loại hình )</t>

--- a/server/excel/release/quest.xlsx
+++ b/server/excel/release/quest.xlsx
@@ -1,24 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="任务库" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="永久历史" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="主线任务" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="日常任务" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="日常任务宝箱" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="周常任务" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="周常任务宝箱" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="成就" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="历练" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Sheet缺少的事件类型" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="Sheet1" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="Sheet4" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="任务库" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="永久历史" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="主线任务" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="日常任务" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="日常任务宝箱" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="周常任务" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="周常任务宝箱" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="成就" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="历练" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet缺少的事件类型" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet4" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -4021,31 +4021,31 @@
     <t xml:space="preserve">7:67000101:1#6:30002:15#3:500015:10</t>
   </si>
   <si>
-    <t xml:space="preserve">Thăng cấp Kiếm Ma đến 6 sao</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thăng cấp Kiếm Ma đến 7 sao</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thăng cấp Kiếm Ma đến 8 sao</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thăng cấp Kiếm Ma đến 9 sao</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thăng cấp Kiếm Ma đến 10 sao</t>
+    <t xml:space="preserve">Thăng Shanks lên 6 sao</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thăng Shanks lên 7 sao</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thăng Shanks lên 8 sao</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thăng Shanks lên 9 sao</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thăng Shanks lên 10 sao</t>
   </si>
   <si>
     <t xml:space="preserve">7:65000101:1#5:4:1#3:100004:10000#3:500011:1</t>
   </si>
   <si>
-    <t xml:space="preserve">Thăng cấp Kiếm Ma đến 11 sao</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thăng cấp Kiếm Ma đến 12 sao</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thăng cấp Kiếm Ma đến 13 sao</t>
+    <t xml:space="preserve">Thăng Shanks lên 11 sao</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thăng Shanks lên 12 sao</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thăng Shanks lên 13 sao</t>
   </si>
   <si>
     <t xml:space="preserve">7:65000101:1#6:30002:15#3:500015:10</t>
